--- a/mainWidget/mainWidget/src/database/计算模型-跌落试验-0.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-跌落试验-0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D88EFB-5303-445E-B412-2231B30F515F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DB21B0-7329-46AD-A24C-DCF8DE1B90E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/mainWidget/mainWidget/src/database/计算模型-跌落试验-0.xlsx
+++ b/mainWidget/mainWidget/src/database/计算模型-跌落试验-0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VSProject\git\GFApp\mainWidget\mainWidget\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DB21B0-7329-46AD-A24C-DCF8DE1B90E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AE30F4-10C1-4B8E-B25F-484B96052151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="1327">
   <si>
     <t>序号</t>
   </si>
@@ -1445,16 +1445,2579 @@
   </si>
   <si>
     <t>-4.8968</t>
+  </si>
+  <si>
+    <t>-45.7665 +0.0143*B + 0.0*C +0.1741*D +0.0406*E +0.0497*F + 0.0*G +0.1421*H +0.0813*I +0.0143*J -0.0963*K +1.0415*L -25.9595*M</t>
+  </si>
+  <si>
+    <t>-45.7665</t>
+  </si>
+  <si>
+    <t>0.0143</t>
+  </si>
+  <si>
+    <t>0.1741</t>
+  </si>
+  <si>
+    <t>0.0406</t>
+  </si>
+  <si>
+    <t>0.0497</t>
+  </si>
+  <si>
+    <t>0.1421</t>
+  </si>
+  <si>
+    <t>0.0813</t>
+  </si>
+  <si>
+    <t>-0.0963</t>
+  </si>
+  <si>
+    <t>1.0415</t>
+  </si>
+  <si>
+    <t>-25.9595</t>
+  </si>
+  <si>
+    <t>-410.0335 +0.0198*B + 0.0*C -0.6976*D -0.0434*E +0.029*F + 0.0*G -0.2167*H +0.0413*I +0.002*J -0.1779*K +1.9774*L -18.4465*M</t>
+  </si>
+  <si>
+    <t>-410.0335</t>
+  </si>
+  <si>
+    <t>0.0198</t>
+  </si>
+  <si>
+    <t>-0.6976</t>
+  </si>
+  <si>
+    <t>-0.0434</t>
+  </si>
+  <si>
+    <t>0.0290</t>
+  </si>
+  <si>
+    <t>-0.2167</t>
+  </si>
+  <si>
+    <t>0.0413</t>
+  </si>
+  <si>
+    <t>0.0020</t>
+  </si>
+  <si>
+    <t>-0.1779</t>
+  </si>
+  <si>
+    <t>1.9774</t>
+  </si>
+  <si>
+    <t>-18.4465</t>
+  </si>
+  <si>
+    <t>-208.2054 +0.0011*B + 0.0*C -0.2317*D +0.0041*E -0.0081*F + 0.0*G +0.4231*H +0.0123*I +0.0066*J -0.1078*K +2.3695*L -11.7353*M</t>
+  </si>
+  <si>
+    <t>-208.2054</t>
+  </si>
+  <si>
+    <t>0.0011</t>
+  </si>
+  <si>
+    <t>-0.2317</t>
+  </si>
+  <si>
+    <t>-0.0081</t>
+  </si>
+  <si>
+    <t>0.4231</t>
+  </si>
+  <si>
+    <t>0.0123</t>
+  </si>
+  <si>
+    <t>0.0066</t>
+  </si>
+  <si>
+    <t>-0.1078</t>
+  </si>
+  <si>
+    <t>2.3695</t>
+  </si>
+  <si>
+    <t>-11.7353</t>
+  </si>
+  <si>
+    <t>-634.0873 +0.0282*B + 0.0*C -0.4619*D +0.0066*E -0.009*F + 0.0*G -0.3621*H +0.0376*I +0.0141*J -0.0409*K +0.374*L -20.8279*M</t>
+  </si>
+  <si>
+    <t>-634.0873</t>
+  </si>
+  <si>
+    <t>0.0282</t>
+  </si>
+  <si>
+    <t>-0.4619</t>
+  </si>
+  <si>
+    <t>-0.0090</t>
+  </si>
+  <si>
+    <t>-0.3621</t>
+  </si>
+  <si>
+    <t>0.0376</t>
+  </si>
+  <si>
+    <t>0.0141</t>
+  </si>
+  <si>
+    <t>-0.0409</t>
+  </si>
+  <si>
+    <t>0.3740</t>
+  </si>
+  <si>
+    <t>-20.8279</t>
+  </si>
+  <si>
+    <t>-793.3563 +0.0059*B + 0.0*C -0.2032*D +0.0285*E +0.0861*F + 0.0*G -0.5625*H +0.0416*I +0.0059*J -0.1143*K +1.1115*L +21.2865*M</t>
+  </si>
+  <si>
+    <t>-793.3563</t>
+  </si>
+  <si>
+    <t>0.0059</t>
+  </si>
+  <si>
+    <t>-0.2032</t>
+  </si>
+  <si>
+    <t>0.0285</t>
+  </si>
+  <si>
+    <t>0.0861</t>
+  </si>
+  <si>
+    <t>-0.5625</t>
+  </si>
+  <si>
+    <t>0.0416</t>
+  </si>
+  <si>
+    <t>-0.1143</t>
+  </si>
+  <si>
+    <t>1.1115</t>
+  </si>
+  <si>
+    <t>21.2865</t>
+  </si>
+  <si>
+    <t>118.7085 +0.0042*B + 0.0*C -0.1516*D +0.0098*E +0.1259*F + 0.0*G +0.0292*H +0.0255*I +0.0006*J -0.1592*K +1.3152*L +31.569*M</t>
+  </si>
+  <si>
+    <t>118.7085</t>
+  </si>
+  <si>
+    <t>-0.1516</t>
+  </si>
+  <si>
+    <t>0.0098</t>
+  </si>
+  <si>
+    <t>0.1259</t>
+  </si>
+  <si>
+    <t>0.0292</t>
+  </si>
+  <si>
+    <t>0.0255</t>
+  </si>
+  <si>
+    <t>-0.1592</t>
+  </si>
+  <si>
+    <t>1.3152</t>
+  </si>
+  <si>
+    <t>31.5690</t>
+  </si>
+  <si>
+    <t>-261.018 +0.0308*B + 0.0*C +0.0767*D -0.0155*E +0.0872*F + 0.0*G +0.9588*H +0.0302*I +0.0202*J -0.2823*K +1.3247*L -8.5566*M</t>
+  </si>
+  <si>
+    <t>-261.0180</t>
+  </si>
+  <si>
+    <t>0.0308</t>
+  </si>
+  <si>
+    <t>0.0767</t>
+  </si>
+  <si>
+    <t>-0.0155</t>
+  </si>
+  <si>
+    <t>0.0872</t>
+  </si>
+  <si>
+    <t>0.9588</t>
+  </si>
+  <si>
+    <t>0.0302</t>
+  </si>
+  <si>
+    <t>-0.2823</t>
+  </si>
+  <si>
+    <t>1.3247</t>
+  </si>
+  <si>
+    <t>-8.5566</t>
+  </si>
+  <si>
+    <t>-346.9322 +0.0176*B + 0.0*C -0.7229*D -0.0045*E +0.0869*F + 0.0*G +0.9311*H +0.0149*I +0.0027*J -0.0991*K +1.4195*L -0.9151*M</t>
+  </si>
+  <si>
+    <t>-346.9322</t>
+  </si>
+  <si>
+    <t>-0.7229</t>
+  </si>
+  <si>
+    <t>0.0869</t>
+  </si>
+  <si>
+    <t>0.9311</t>
+  </si>
+  <si>
+    <t>0.0149</t>
+  </si>
+  <si>
+    <t>0.0027</t>
+  </si>
+  <si>
+    <t>-0.0991</t>
+  </si>
+  <si>
+    <t>1.4195</t>
+  </si>
+  <si>
+    <t>-0.9151</t>
+  </si>
+  <si>
+    <t>-434.2678 +0.0237*B + 0.0*C -0.0133*D +0.0262*E +0.0202*F + 0.0*G +0.099*H +0.0189*I +0.0006*J -0.0301*K +0.756*L -11.1469*M</t>
+  </si>
+  <si>
+    <t>-434.2678</t>
+  </si>
+  <si>
+    <t>-0.0133</t>
+  </si>
+  <si>
+    <t>0.0262</t>
+  </si>
+  <si>
+    <t>0.0990</t>
+  </si>
+  <si>
+    <t>0.0189</t>
+  </si>
+  <si>
+    <t>-0.0301</t>
+  </si>
+  <si>
+    <t>0.7560</t>
+  </si>
+  <si>
+    <t>-11.1469</t>
+  </si>
+  <si>
+    <t>-322.5503 +0.0011*B + 0.0*C -0.1896*D -0.0077*E +0.0139*F + 0.0*G +0.1757*H +0.0441*I +0.0226*J -0.0406*K +0.7525*L -13.6622*M</t>
+  </si>
+  <si>
+    <t>-322.5503</t>
+  </si>
+  <si>
+    <t>-0.1896</t>
+  </si>
+  <si>
+    <t>0.0139</t>
+  </si>
+  <si>
+    <t>0.1757</t>
+  </si>
+  <si>
+    <t>0.0441</t>
+  </si>
+  <si>
+    <t>-0.0406</t>
+  </si>
+  <si>
+    <t>0.7525</t>
+  </si>
+  <si>
+    <t>-13.6622</t>
+  </si>
+  <si>
+    <t>-959.9824 +0.0159*B + 0.0*C -0.0259*D +0.0649*E +0.0523*F + 0.0*G +0.389*H +0.0302*I +0.0006*J +0.0431*K +1.2537*L +13.6999*M</t>
+  </si>
+  <si>
+    <t>-959.9824</t>
+  </si>
+  <si>
+    <t>0.0159</t>
+  </si>
+  <si>
+    <t>-0.0259</t>
+  </si>
+  <si>
+    <t>0.0649</t>
+  </si>
+  <si>
+    <t>0.0523</t>
+  </si>
+  <si>
+    <t>0.3890</t>
+  </si>
+  <si>
+    <t>0.0431</t>
+  </si>
+  <si>
+    <t>1.2537</t>
+  </si>
+  <si>
+    <t>13.6999</t>
+  </si>
+  <si>
+    <t>-577.9496 +0.0366*B + 0.0*C -0.5235*D +0.0164*E +0.2024*F + 0.0*G -0.2065*H +0.0134*I +0.0094*J -0.0993*K -1.081*L -9.1409*M</t>
+  </si>
+  <si>
+    <t>-577.9496</t>
+  </si>
+  <si>
+    <t>0.0366</t>
+  </si>
+  <si>
+    <t>-0.5235</t>
+  </si>
+  <si>
+    <t>0.0164</t>
+  </si>
+  <si>
+    <t>0.2024</t>
+  </si>
+  <si>
+    <t>-0.2065</t>
+  </si>
+  <si>
+    <t>0.0134</t>
+  </si>
+  <si>
+    <t>-0.0993</t>
+  </si>
+  <si>
+    <t>-1.0810</t>
+  </si>
+  <si>
+    <t>-9.1409</t>
+  </si>
+  <si>
+    <t>-635.8255 +0.0232*B + 0.0*C -0.3593*D +0.0413*E +0.0151*F + 0.0*G +0.1016*H +0.0571*I +0.0006*J -0.0361*K +1.8167*L -62.1291*M</t>
+  </si>
+  <si>
+    <t>-635.8255</t>
+  </si>
+  <si>
+    <t>-0.3593</t>
+  </si>
+  <si>
+    <t>0.0151</t>
+  </si>
+  <si>
+    <t>0.1016</t>
+  </si>
+  <si>
+    <t>0.0571</t>
+  </si>
+  <si>
+    <t>-0.0361</t>
+  </si>
+  <si>
+    <t>1.8167</t>
+  </si>
+  <si>
+    <t>-62.1291</t>
+  </si>
+  <si>
+    <t>-163.8831 +0.0201*B + 0.0*C +0.2197*D -0.0308*E -0.009*F + 0.0*G +0.4905*H +0.0407*I +0.0105*J -0.0258*K -0.1982*L -3.9659*M</t>
+  </si>
+  <si>
+    <t>-163.8831</t>
+  </si>
+  <si>
+    <t>0.0201</t>
+  </si>
+  <si>
+    <t>0.2197</t>
+  </si>
+  <si>
+    <t>-0.0308</t>
+  </si>
+  <si>
+    <t>0.4905</t>
+  </si>
+  <si>
+    <t>0.0105</t>
+  </si>
+  <si>
+    <t>-0.0258</t>
+  </si>
+  <si>
+    <t>-0.1982</t>
+  </si>
+  <si>
+    <t>-3.9659</t>
+  </si>
+  <si>
+    <t>-122.8411 +0.006*B + 0.0*C +0.5887*D +0.0135*E -0.009*F + 0.0*G +0.5526*H +0.0005*I +0.0145*J +0.0445*K -0.3408*L +19.1486*M</t>
+  </si>
+  <si>
+    <t>-122.8411</t>
+  </si>
+  <si>
+    <t>0.0060</t>
+  </si>
+  <si>
+    <t>0.5887</t>
+  </si>
+  <si>
+    <t>0.0135</t>
+  </si>
+  <si>
+    <t>0.5526</t>
+  </si>
+  <si>
+    <t>0.0145</t>
+  </si>
+  <si>
+    <t>0.0445</t>
+  </si>
+  <si>
+    <t>-0.3408</t>
+  </si>
+  <si>
+    <t>19.1486</t>
+  </si>
+  <si>
+    <t>-77.5337 +0.0282*B + 0.0*C +0.5992*D -0.0051*E +0.0169*F + 0.0*G -0.1599*H +0.0055*I +0.0081*J -0.0262*K +0.7719*L +14.8428*M</t>
+  </si>
+  <si>
+    <t>-77.5337</t>
+  </si>
+  <si>
+    <t>0.5992</t>
+  </si>
+  <si>
+    <t>-0.0051</t>
+  </si>
+  <si>
+    <t>-0.1599</t>
+  </si>
+  <si>
+    <t>-0.0262</t>
+  </si>
+  <si>
+    <t>0.7719</t>
+  </si>
+  <si>
+    <t>14.8428</t>
+  </si>
+  <si>
+    <t>-228.8425 +0.0374*B + 0.0*C -0.1365*D +0.0715*E +0.1038*F + 0.0*G -0.145*H -0.0026*I +0.0122*J -0.0751*K +1.2153*L +3.6529*M</t>
+  </si>
+  <si>
+    <t>-228.8425</t>
+  </si>
+  <si>
+    <t>0.0374</t>
+  </si>
+  <si>
+    <t>-0.1365</t>
+  </si>
+  <si>
+    <t>0.1038</t>
+  </si>
+  <si>
+    <t>-0.1450</t>
+  </si>
+  <si>
+    <t>-0.0026</t>
+  </si>
+  <si>
+    <t>0.0122</t>
+  </si>
+  <si>
+    <t>-0.0751</t>
+  </si>
+  <si>
+    <t>1.2153</t>
+  </si>
+  <si>
+    <t>3.6529</t>
+  </si>
+  <si>
+    <t>-261.3279 +0.004*B + 0.0*C -0.562*D -0.0103*E +0.1184*F + 0.0*G +0.3487*H -0.0081*I +0.01*J -0.0224*K -0.4049*L -6.4485*M</t>
+  </si>
+  <si>
+    <t>-261.3279</t>
+  </si>
+  <si>
+    <t>0.0040</t>
+  </si>
+  <si>
+    <t>-0.5620</t>
+  </si>
+  <si>
+    <t>-0.0103</t>
+  </si>
+  <si>
+    <t>0.1184</t>
+  </si>
+  <si>
+    <t>0.3487</t>
+  </si>
+  <si>
+    <t>0.0100</t>
+  </si>
+  <si>
+    <t>-0.0224</t>
+  </si>
+  <si>
+    <t>-0.4049</t>
+  </si>
+  <si>
+    <t>-6.4485</t>
+  </si>
+  <si>
+    <t>-211.7326 +0.0011*B + 0.0*C +0.0754*D +0.0157*E +0.1327*F + 0.0*G +0.7356*H -0.0123*I +0.0018*J -0.0112*K +1.0123*L +4.9747*M</t>
+  </si>
+  <si>
+    <t>-211.7326</t>
+  </si>
+  <si>
+    <t>0.0754</t>
+  </si>
+  <si>
+    <t>0.0157</t>
+  </si>
+  <si>
+    <t>0.1327</t>
+  </si>
+  <si>
+    <t>0.7356</t>
+  </si>
+  <si>
+    <t>-0.0123</t>
+  </si>
+  <si>
+    <t>-0.0112</t>
+  </si>
+  <si>
+    <t>1.0123</t>
+  </si>
+  <si>
+    <t>4.9747</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0246*B + 0.0*C +0.3401*D +0.0259*E +0.1055*F + 0.0*G +0.1047*H +0.0554*I +0.003*J -0.0762*K -0.0008*L -8.7201*M</t>
+  </si>
+  <si>
+    <t>168.6442</t>
+  </si>
+  <si>
+    <t>0.0246</t>
+  </si>
+  <si>
+    <t>0.3401</t>
+  </si>
+  <si>
+    <t>0.0259</t>
+  </si>
+  <si>
+    <t>0.1055</t>
+  </si>
+  <si>
+    <t>0.1047</t>
+  </si>
+  <si>
+    <t>0.0554</t>
+  </si>
+  <si>
+    <t>0.0030</t>
+  </si>
+  <si>
+    <t>-0.0762</t>
+  </si>
+  <si>
+    <t>-0.0008</t>
+  </si>
+  <si>
+    <t>-8.7201</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0011*B + 0.0*C +0.1872*D -0.0405*E +0.0347*F + 0.0*G +0.7518*H +0.0334*I +0.0008*J -0.1176*K +1.1804*L -34.3991*M</t>
+  </si>
+  <si>
+    <t>0.1872</t>
+  </si>
+  <si>
+    <t>-0.0405</t>
+  </si>
+  <si>
+    <t>0.7518</t>
+  </si>
+  <si>
+    <t>0.0334</t>
+  </si>
+  <si>
+    <t>-0.1176</t>
+  </si>
+  <si>
+    <t>1.1804</t>
+  </si>
+  <si>
+    <t>-34.3991</t>
+  </si>
+  <si>
+    <t>-151.838 +0.017*B + 0.0*C -0.2682*D +0.0566*E +0.1044*F + 0.0*G -0.6832*H +0.0372*I +0.0038*J +0.018*K -0.3123*L -14.9359*M</t>
+  </si>
+  <si>
+    <t>-151.8380</t>
+  </si>
+  <si>
+    <t>0.0170</t>
+  </si>
+  <si>
+    <t>-0.2682</t>
+  </si>
+  <si>
+    <t>0.0566</t>
+  </si>
+  <si>
+    <t>0.1044</t>
+  </si>
+  <si>
+    <t>-0.6832</t>
+  </si>
+  <si>
+    <t>0.0372</t>
+  </si>
+  <si>
+    <t>0.0180</t>
+  </si>
+  <si>
+    <t>-0.3123</t>
+  </si>
+  <si>
+    <t>-14.9359</t>
+  </si>
+  <si>
+    <t>-42.6353 +0.0289*B + 0.0*C -0.4549*D -0.0074*E +0.0345*F + 0.0*G -0.0511*H +0.0872*I +0.0117*J -0.1648*K +1.422*L +55.7834*M</t>
+  </si>
+  <si>
+    <t>-42.6353</t>
+  </si>
+  <si>
+    <t>0.0289</t>
+  </si>
+  <si>
+    <t>-0.4549</t>
+  </si>
+  <si>
+    <t>-0.0074</t>
+  </si>
+  <si>
+    <t>0.0345</t>
+  </si>
+  <si>
+    <t>-0.0511</t>
+  </si>
+  <si>
+    <t>-0.1648</t>
+  </si>
+  <si>
+    <t>1.4220</t>
+  </si>
+  <si>
+    <t>55.7834</t>
+  </si>
+  <si>
+    <t>157.0052 +0.0011*B + 0.0*C -0.2112*D +0.034*E +0.0198*F + 0.0*G +0.4545*H +0.0559*I +0.0019*J -0.0609*K -1.1317*L -43.6946*M</t>
+  </si>
+  <si>
+    <t>157.0052</t>
+  </si>
+  <si>
+    <t>-0.2112</t>
+  </si>
+  <si>
+    <t>0.0340</t>
+  </si>
+  <si>
+    <t>0.4545</t>
+  </si>
+  <si>
+    <t>0.0559</t>
+  </si>
+  <si>
+    <t>0.0019</t>
+  </si>
+  <si>
+    <t>-0.0609</t>
+  </si>
+  <si>
+    <t>-1.1317</t>
+  </si>
+  <si>
+    <t>-43.6946</t>
+  </si>
+  <si>
+    <t>-329.3558 +0.0011*B + 0.0*C +0.5093*D -0.0358*E +0.0367*F + 0.0*G +0.3103*H +0.077*I +0.0006*J +0.0449*K +0.5017*L -42.3389*M</t>
+  </si>
+  <si>
+    <t>-329.3558</t>
+  </si>
+  <si>
+    <t>0.5093</t>
+  </si>
+  <si>
+    <t>-0.0358</t>
+  </si>
+  <si>
+    <t>0.0367</t>
+  </si>
+  <si>
+    <t>0.3103</t>
+  </si>
+  <si>
+    <t>0.0770</t>
+  </si>
+  <si>
+    <t>0.0449</t>
+  </si>
+  <si>
+    <t>0.5017</t>
+  </si>
+  <si>
+    <t>-42.3389</t>
+  </si>
+  <si>
+    <t>-58.866 +0.0192*B + 0.0*C -0.2507*D +0.003*E +0.0402*F + 0.0*G +0.3023*H +0.0523*I +0.0204*J -0.1628*K +2.6541*L -73.0238*M</t>
+  </si>
+  <si>
+    <t>-58.8660</t>
+  </si>
+  <si>
+    <t>0.0192</t>
+  </si>
+  <si>
+    <t>-0.2507</t>
+  </si>
+  <si>
+    <t>0.0402</t>
+  </si>
+  <si>
+    <t>0.3023</t>
+  </si>
+  <si>
+    <t>0.0204</t>
+  </si>
+  <si>
+    <t>-0.1628</t>
+  </si>
+  <si>
+    <t>2.6541</t>
+  </si>
+  <si>
+    <t>-73.0238</t>
+  </si>
+  <si>
+    <t>-291.2113 +0.0248*B + 0.0*C +0.0493*D -0.0149*E +0.0513*F + 0.0*G +0.0228*H +0.0127*I +0.0149*J -0.0248*K -0.2113*L +17.1323*M</t>
+  </si>
+  <si>
+    <t>-291.2113</t>
+  </si>
+  <si>
+    <t>0.0493</t>
+  </si>
+  <si>
+    <t>-0.0149</t>
+  </si>
+  <si>
+    <t>0.0513</t>
+  </si>
+  <si>
+    <t>0.0127</t>
+  </si>
+  <si>
+    <t>-0.0248</t>
+  </si>
+  <si>
+    <t>-0.2113</t>
+  </si>
+  <si>
+    <t>17.1323</t>
+  </si>
+  <si>
+    <t>-117.4564 +0.0281*B + 0.0*C +0.1679*D -0.0202*E +0.0291*F + 0.0*G +0.5944*H +0.0507*I +0.0085*J -0.0456*K +1.7868*L -30.0111*M</t>
+  </si>
+  <si>
+    <t>-117.4564</t>
+  </si>
+  <si>
+    <t>0.0281</t>
+  </si>
+  <si>
+    <t>0.1679</t>
+  </si>
+  <si>
+    <t>-0.0202</t>
+  </si>
+  <si>
+    <t>0.5944</t>
+  </si>
+  <si>
+    <t>0.0507</t>
+  </si>
+  <si>
+    <t>-0.0456</t>
+  </si>
+  <si>
+    <t>1.7868</t>
+  </si>
+  <si>
+    <t>-30.0111</t>
+  </si>
+  <si>
+    <t>-26.6974 +0.0134*B + 0.0*C -0.1205*D +0.0296*E +0.1164*F + 0.0*G +0.6249*H +0.0727*I +0.0089*J +0.0033*K +0.1767*L -1.06*M</t>
+  </si>
+  <si>
+    <t>-26.6974</t>
+  </si>
+  <si>
+    <t>-0.1205</t>
+  </si>
+  <si>
+    <t>0.0296</t>
+  </si>
+  <si>
+    <t>0.1164</t>
+  </si>
+  <si>
+    <t>0.6249</t>
+  </si>
+  <si>
+    <t>0.0089</t>
+  </si>
+  <si>
+    <t>0.1767</t>
+  </si>
+  <si>
+    <t>-1.0600</t>
+  </si>
+  <si>
+    <t>-283.0202 +0.0177*B + 0.0*C +0.1562*D -0.02*E +0.1963*F + 0.0*G -0.2136*H -0.0071*I +0.0172*J +0.0127*K +1.1241*L +8.5566*M</t>
+  </si>
+  <si>
+    <t>-283.0202</t>
+  </si>
+  <si>
+    <t>0.0177</t>
+  </si>
+  <si>
+    <t>0.1562</t>
+  </si>
+  <si>
+    <t>-0.0200</t>
+  </si>
+  <si>
+    <t>0.1963</t>
+  </si>
+  <si>
+    <t>-0.2136</t>
+  </si>
+  <si>
+    <t>-0.0071</t>
+  </si>
+  <si>
+    <t>0.0172</t>
+  </si>
+  <si>
+    <t>1.1241</t>
+  </si>
+  <si>
+    <t>8.5566</t>
+  </si>
+  <si>
+    <t>-238.3987 +0.0033*B + 0.0*C -0.0206*D -0.0163*E +0.1259*F + 0.0*G +0.1822*H +0.0052*I +0.0063*J -0.02*K -0.0803*L -37.303*M</t>
+  </si>
+  <si>
+    <t>-238.3987</t>
+  </si>
+  <si>
+    <t>-0.0206</t>
+  </si>
+  <si>
+    <t>-0.0163</t>
+  </si>
+  <si>
+    <t>0.1822</t>
+  </si>
+  <si>
+    <t>-0.0803</t>
+  </si>
+  <si>
+    <t>-37.3030</t>
+  </si>
+  <si>
+    <t>-141.5325 +0.0199*B + 0.0*C -0.2189*D -0.011*E +0.079*F + 0.0*G -0.4173*H -0.0132*I +0.0034*J -0.0742*K +0.8066*L +35.3348*M</t>
+  </si>
+  <si>
+    <t>-141.5325</t>
+  </si>
+  <si>
+    <t>0.0199</t>
+  </si>
+  <si>
+    <t>-0.2189</t>
+  </si>
+  <si>
+    <t>-0.0110</t>
+  </si>
+  <si>
+    <t>0.0790</t>
+  </si>
+  <si>
+    <t>-0.4173</t>
+  </si>
+  <si>
+    <t>-0.0132</t>
+  </si>
+  <si>
+    <t>0.0034</t>
+  </si>
+  <si>
+    <t>-0.0742</t>
+  </si>
+  <si>
+    <t>0.8066</t>
+  </si>
+  <si>
+    <t>35.3348</t>
+  </si>
+  <si>
+    <t>90.8445 +0.014*B + 0.0*C -0.0529*D -0.0247*E +0.0633*F + 0.0*G +0.117*H +0.0416*I +0.0026*J -0.0108*K +2.0455*L -14.747*M</t>
+  </si>
+  <si>
+    <t>90.8445</t>
+  </si>
+  <si>
+    <t>0.0140</t>
+  </si>
+  <si>
+    <t>-0.0529</t>
+  </si>
+  <si>
+    <t>-0.0247</t>
+  </si>
+  <si>
+    <t>0.0633</t>
+  </si>
+  <si>
+    <t>0.1170</t>
+  </si>
+  <si>
+    <t>-0.0108</t>
+  </si>
+  <si>
+    <t>2.0455</t>
+  </si>
+  <si>
+    <t>-14.7470</t>
+  </si>
+  <si>
+    <t>-81.7232 +0.0263*B + 0.0*C -0.1829*D +0.007*E +0.0652*F + 0.0*G +0.295*H +0.0069*I +0.0089*J -0.0127*K +1.9627*L +19.0188*M</t>
+  </si>
+  <si>
+    <t>-81.7232</t>
+  </si>
+  <si>
+    <t>0.0263</t>
+  </si>
+  <si>
+    <t>-0.1829</t>
+  </si>
+  <si>
+    <t>0.0070</t>
+  </si>
+  <si>
+    <t>0.0652</t>
+  </si>
+  <si>
+    <t>0.2950</t>
+  </si>
+  <si>
+    <t>0.0069</t>
+  </si>
+  <si>
+    <t>-0.0127</t>
+  </si>
+  <si>
+    <t>1.9627</t>
+  </si>
+  <si>
+    <t>19.0188</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0052*B + 0.0*C +0.2505*D +0.0059*E +0.2024*F + 0.0*G -0.1225*H +0.0047*I +0.0043*J -0.2394*K -0.0418*L -35.3085*M</t>
+  </si>
+  <si>
+    <t>0.2505</t>
+  </si>
+  <si>
+    <t>-0.1225</t>
+  </si>
+  <si>
+    <t>-0.2394</t>
+  </si>
+  <si>
+    <t>-0.0418</t>
+  </si>
+  <si>
+    <t>-35.3085</t>
+  </si>
+  <si>
+    <t>-176.8423 +0.0213*B + 0.0*C +0.5922*D +0.0258*E +0.0281*F + 0.0*G -0.164*H +0.0469*I +0.0006*J +0.1027*K +1.6872*L -26.1415*M</t>
+  </si>
+  <si>
+    <t>-176.8423</t>
+  </si>
+  <si>
+    <t>0.0213</t>
+  </si>
+  <si>
+    <t>0.5922</t>
+  </si>
+  <si>
+    <t>0.0258</t>
+  </si>
+  <si>
+    <t>-0.1640</t>
+  </si>
+  <si>
+    <t>0.0469</t>
+  </si>
+  <si>
+    <t>0.1027</t>
+  </si>
+  <si>
+    <t>1.6872</t>
+  </si>
+  <si>
+    <t>-26.1415</t>
+  </si>
+  <si>
+    <t>-882.1528 +0.0359*B + 0.0*C -0.0854*D +0.0332*E -0.009*F + 0.0*G -0.0262*H +0.0315*I +0.009*J -0.0947*K +1.1229*L -45.0614*M</t>
+  </si>
+  <si>
+    <t>-882.1528</t>
+  </si>
+  <si>
+    <t>0.0359</t>
+  </si>
+  <si>
+    <t>-0.0854</t>
+  </si>
+  <si>
+    <t>0.0332</t>
+  </si>
+  <si>
+    <t>0.0315</t>
+  </si>
+  <si>
+    <t>0.0090</t>
+  </si>
+  <si>
+    <t>-0.0947</t>
+  </si>
+  <si>
+    <t>1.1229</t>
+  </si>
+  <si>
+    <t>-45.0614</t>
+  </si>
+  <si>
+    <t>-287.6515 +0.0181*B + 0.0*C +0.1287*D +0.0196*E -0.0064*F + 0.0*G -0.457*H +0.0718*I +0.0111*J -0.1205*K +2.0641*L -7.6515*M</t>
+  </si>
+  <si>
+    <t>-287.6515</t>
+  </si>
+  <si>
+    <t>0.0181</t>
+  </si>
+  <si>
+    <t>0.1287</t>
+  </si>
+  <si>
+    <t>0.0196</t>
+  </si>
+  <si>
+    <t>-0.0064</t>
+  </si>
+  <si>
+    <t>-0.4570</t>
+  </si>
+  <si>
+    <t>0.0718</t>
+  </si>
+  <si>
+    <t>0.0111</t>
+  </si>
+  <si>
+    <t>2.0641</t>
+  </si>
+  <si>
+    <t>-7.6515</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0173*B + 0.0*C +0.6551*D +0.0466*E +0.0487*F + 0.0*G +0.6977*H +0.0518*I +0.0188*J -0.1392*K +1.1869*L +22.1535*M</t>
+  </si>
+  <si>
+    <t>0.0173</t>
+  </si>
+  <si>
+    <t>0.6551</t>
+  </si>
+  <si>
+    <t>0.0466</t>
+  </si>
+  <si>
+    <t>0.6977</t>
+  </si>
+  <si>
+    <t>0.0518</t>
+  </si>
+  <si>
+    <t>0.0188</t>
+  </si>
+  <si>
+    <t>-0.1392</t>
+  </si>
+  <si>
+    <t>1.1869</t>
+  </si>
+  <si>
+    <t>22.1535</t>
+  </si>
+  <si>
+    <t>-899.4134 +0.0011*B + 0.0*C -0.7405*D -0.0058*E +0.1096*F + 0.0*G +0.9423*H +0.0337*I +0.0207*J -0.1751*K -1.1317*L -13.0647*M</t>
+  </si>
+  <si>
+    <t>-899.4134</t>
+  </si>
+  <si>
+    <t>-0.7405</t>
+  </si>
+  <si>
+    <t>0.1096</t>
+  </si>
+  <si>
+    <t>0.9423</t>
+  </si>
+  <si>
+    <t>0.0337</t>
+  </si>
+  <si>
+    <t>-0.1751</t>
+  </si>
+  <si>
+    <t>-13.0647</t>
+  </si>
+  <si>
+    <t>-88.402 +0.0158*B + 0.0*C -0.7501*D -0.0011*E -0.009*F + 0.0*G +0.5586*H +0.0429*I +0.0018*J -0.1002*K -0.5827*L -13.2901*M</t>
+  </si>
+  <si>
+    <t>-88.4020</t>
+  </si>
+  <si>
+    <t>0.0158</t>
+  </si>
+  <si>
+    <t>-0.7501</t>
+  </si>
+  <si>
+    <t>0.5586</t>
+  </si>
+  <si>
+    <t>0.0429</t>
+  </si>
+  <si>
+    <t>-0.1002</t>
+  </si>
+  <si>
+    <t>-0.5827</t>
+  </si>
+  <si>
+    <t>-13.2901</t>
+  </si>
+  <si>
+    <t>127.7399 +0.002*B + 0.0*C +0.1252*D -0.0125*E +0.0145*F + 0.0*G +0.2007*H -0.0014*I +0.0046*J -0.1593*K +2.4835*L -10.1937*M</t>
+  </si>
+  <si>
+    <t>127.7399</t>
+  </si>
+  <si>
+    <t>0.1252</t>
+  </si>
+  <si>
+    <t>-0.0125</t>
+  </si>
+  <si>
+    <t>0.2007</t>
+  </si>
+  <si>
+    <t>-0.0014</t>
+  </si>
+  <si>
+    <t>0.0046</t>
+  </si>
+  <si>
+    <t>-0.1593</t>
+  </si>
+  <si>
+    <t>2.4835</t>
+  </si>
+  <si>
+    <t>-10.1937</t>
+  </si>
+  <si>
+    <t>-498.5965 +0.0194*B + 0.0*C -0.0846*D -0.0045*E +0.1031*F + 0.0*G +0.5991*H +0.0145*I +0.0045*J -0.0795*K -1.1317*L -59.2113*M</t>
+  </si>
+  <si>
+    <t>-498.5965</t>
+  </si>
+  <si>
+    <t>-0.0846</t>
+  </si>
+  <si>
+    <t>0.1031</t>
+  </si>
+  <si>
+    <t>0.5991</t>
+  </si>
+  <si>
+    <t>0.0045</t>
+  </si>
+  <si>
+    <t>-59.2113</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0401*B + 0.0*C -0.1311*D +0.0161*E +0.084*F + 0.0*G +1.6688*H +0.0668*I +0.0078*J -0.1384*K -1.1317*L -4.876*M</t>
+  </si>
+  <si>
+    <t>0.0401</t>
+  </si>
+  <si>
+    <t>-0.1311</t>
+  </si>
+  <si>
+    <t>0.0840</t>
+  </si>
+  <si>
+    <t>1.6688</t>
+  </si>
+  <si>
+    <t>0.0668</t>
+  </si>
+  <si>
+    <t>0.0078</t>
+  </si>
+  <si>
+    <t>-0.1384</t>
+  </si>
+  <si>
+    <t>-4.8760</t>
+  </si>
+  <si>
+    <t>-520.0281 +0.0011*B + 0.0*C -0.2665*D -0.0268*E +0.1707*F + 0.0*G +0.6563*H +0.0311*I +0.0196*J -0.049*K -0.382*L +36.845*M</t>
+  </si>
+  <si>
+    <t>-520.0281</t>
+  </si>
+  <si>
+    <t>-0.2665</t>
+  </si>
+  <si>
+    <t>-0.0268</t>
+  </si>
+  <si>
+    <t>0.1707</t>
+  </si>
+  <si>
+    <t>0.6563</t>
+  </si>
+  <si>
+    <t>0.0311</t>
+  </si>
+  <si>
+    <t>-0.0490</t>
+  </si>
+  <si>
+    <t>-0.3820</t>
+  </si>
+  <si>
+    <t>36.8450</t>
+  </si>
+  <si>
+    <t>-29.7962 +0.0013*B + 0.0*C -0.1112*D -0.0214*E -0.009*F + 0.0*G +0.6768*H +0.0918*I +0.0006*J -0.007*K -0.1684*L -26.709*M</t>
+  </si>
+  <si>
+    <t>-29.7962</t>
+  </si>
+  <si>
+    <t>-0.1112</t>
+  </si>
+  <si>
+    <t>-0.0214</t>
+  </si>
+  <si>
+    <t>0.6768</t>
+  </si>
+  <si>
+    <t>0.0918</t>
+  </si>
+  <si>
+    <t>-0.0070</t>
+  </si>
+  <si>
+    <t>-0.1684</t>
+  </si>
+  <si>
+    <t>-26.7090</t>
+  </si>
+  <si>
+    <t>-457.9735 +0.0038*B + 0.0*C -0.0299*D -0.0203*E +0.0815*F + 0.0*G +0.2269*H +0.0238*I +0.002*J -0.1056*K +1.2573*L +4.5279*M</t>
+  </si>
+  <si>
+    <t>-457.9735</t>
+  </si>
+  <si>
+    <t>-0.0299</t>
+  </si>
+  <si>
+    <t>-0.0203</t>
+  </si>
+  <si>
+    <t>0.0815</t>
+  </si>
+  <si>
+    <t>0.2269</t>
+  </si>
+  <si>
+    <t>0.0238</t>
+  </si>
+  <si>
+    <t>-0.1056</t>
+  </si>
+  <si>
+    <t>1.2573</t>
+  </si>
+  <si>
+    <t>4.5279</t>
+  </si>
+  <si>
+    <t>-603.7498 +0.0177*B + 0.0*C +0.2094*D -0.042*E +0.0987*F + 0.0*G -0.0554*H +0.0494*I +0.0031*J -0.2119*K -1.1317*L -9.7883*M</t>
+  </si>
+  <si>
+    <t>-603.7498</t>
+  </si>
+  <si>
+    <t>0.2094</t>
+  </si>
+  <si>
+    <t>-0.0420</t>
+  </si>
+  <si>
+    <t>0.0987</t>
+  </si>
+  <si>
+    <t>-0.0554</t>
+  </si>
+  <si>
+    <t>0.0494</t>
+  </si>
+  <si>
+    <t>-0.2119</t>
+  </si>
+  <si>
+    <t>-9.7883</t>
+  </si>
+  <si>
+    <t>-135.4634 +0.0032*B + 0.0*C +0.171*D -0.0418*E +0.0603*F + 0.0*G -0.3081*H +0.0107*I +0.009*J -0.1302*K +0.1014*L +20.5054*M</t>
+  </si>
+  <si>
+    <t>-135.4634</t>
+  </si>
+  <si>
+    <t>0.0032</t>
+  </si>
+  <si>
+    <t>0.1710</t>
+  </si>
+  <si>
+    <t>0.0603</t>
+  </si>
+  <si>
+    <t>-0.3081</t>
+  </si>
+  <si>
+    <t>0.0107</t>
+  </si>
+  <si>
+    <t>-0.1302</t>
+  </si>
+  <si>
+    <t>0.1014</t>
+  </si>
+  <si>
+    <t>20.5054</t>
+  </si>
+  <si>
+    <t>-452.1063 +0.0284*B + 0.0*C -0.4309*D +0.0149*E +0.1553*F + 0.0*G -0.6962*H +0.0061*I +0.0129*J -0.0733*K +0.8676*L -30.4035*M</t>
+  </si>
+  <si>
+    <t>-452.1063</t>
+  </si>
+  <si>
+    <t>0.0284</t>
+  </si>
+  <si>
+    <t>-0.4309</t>
+  </si>
+  <si>
+    <t>0.1553</t>
+  </si>
+  <si>
+    <t>-0.6962</t>
+  </si>
+  <si>
+    <t>0.0061</t>
+  </si>
+  <si>
+    <t>-0.0733</t>
+  </si>
+  <si>
+    <t>0.8676</t>
+  </si>
+  <si>
+    <t>-30.4035</t>
+  </si>
+  <si>
+    <t>-200.9909 +0.0141*B + 0.0*C +0.3511*D +0.0078*E +0.0857*F + 0.0*G +0.0602*H +0.0159*I +0.0055*J -0.0216*K +0.0644*L -2.1473*M</t>
+  </si>
+  <si>
+    <t>-200.9909</t>
+  </si>
+  <si>
+    <t>0.3511</t>
+  </si>
+  <si>
+    <t>0.0857</t>
+  </si>
+  <si>
+    <t>0.0602</t>
+  </si>
+  <si>
+    <t>-0.0216</t>
+  </si>
+  <si>
+    <t>0.0644</t>
+  </si>
+  <si>
+    <t>-2.1473</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0289*B + 0.0*C -0.1574*D +0.0323*E +0.0387*F + 0.0*G -0.6892*H -0.0006*I +0.0006*J -0.0861*K +0.51*L +41.692*M</t>
+  </si>
+  <si>
+    <t>-0.1574</t>
+  </si>
+  <si>
+    <t>0.0387</t>
+  </si>
+  <si>
+    <t>-0.6892</t>
+  </si>
+  <si>
+    <t>-0.0006</t>
+  </si>
+  <si>
+    <t>-0.0861</t>
+  </si>
+  <si>
+    <t>0.5100</t>
+  </si>
+  <si>
+    <t>41.6920</t>
+  </si>
+  <si>
+    <t>-110.0276 +0.0131*B + 0.0*C +0.2359*D -0.056*E +0.0793*F + 0.0*G +0.6052*H -0.0155*I +0.0171*J -0.0265*K +0.0702*L +8.6968*M</t>
+  </si>
+  <si>
+    <t>-110.0276</t>
+  </si>
+  <si>
+    <t>0.0131</t>
+  </si>
+  <si>
+    <t>0.2359</t>
+  </si>
+  <si>
+    <t>-0.0560</t>
+  </si>
+  <si>
+    <t>0.0793</t>
+  </si>
+  <si>
+    <t>0.6052</t>
+  </si>
+  <si>
+    <t>0.0171</t>
+  </si>
+  <si>
+    <t>-0.0265</t>
+  </si>
+  <si>
+    <t>0.0702</t>
+  </si>
+  <si>
+    <t>8.6968</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0189*B + 0.0*C +0.0381*D -0.0107*E +0.0109*F + 0.0*G +0.6326*H +0.0042*I +0.0092*J -0.097*K +0.977*L -0.7598*M</t>
+  </si>
+  <si>
+    <t>0.0381</t>
+  </si>
+  <si>
+    <t>-0.0107</t>
+  </si>
+  <si>
+    <t>0.0109</t>
+  </si>
+  <si>
+    <t>0.6326</t>
+  </si>
+  <si>
+    <t>0.0092</t>
+  </si>
+  <si>
+    <t>-0.0970</t>
+  </si>
+  <si>
+    <t>0.9770</t>
+  </si>
+  <si>
+    <t>-0.7598</t>
+  </si>
+  <si>
+    <t>158.9259 +0.0089*B + 0.0*C -0.1382*D -0.0241*E +0.0364*F + 0.0*G +0.4239*H +0.0553*I +0.0019*J +0.0195*K +1.8659*L +1.7622*M</t>
+  </si>
+  <si>
+    <t>158.9259</t>
+  </si>
+  <si>
+    <t>-0.1382</t>
+  </si>
+  <si>
+    <t>-0.0241</t>
+  </si>
+  <si>
+    <t>0.0364</t>
+  </si>
+  <si>
+    <t>0.4239</t>
+  </si>
+  <si>
+    <t>0.0553</t>
+  </si>
+  <si>
+    <t>1.8659</t>
+  </si>
+  <si>
+    <t>1.7622</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0051*B + 0.0*C -0.47*D -0.0448*E +0.1587*F + 0.0*G +0.5516*H +0.0296*I +0.0108*J -0.1531*K +2.9712*L -7.2232*M</t>
+  </si>
+  <si>
+    <t>-0.4700</t>
+  </si>
+  <si>
+    <t>-0.0448</t>
+  </si>
+  <si>
+    <t>0.1587</t>
+  </si>
+  <si>
+    <t>0.5516</t>
+  </si>
+  <si>
+    <t>0.0108</t>
+  </si>
+  <si>
+    <t>-0.1531</t>
+  </si>
+  <si>
+    <t>2.9712</t>
+  </si>
+  <si>
+    <t>-7.2232</t>
+  </si>
+  <si>
+    <t>-192.3596 +0.0268*B + 0.0*C +0.1173*D +0.007*E +0.0146*F + 0.0*G +0.4673*H +0.0909*I +0.0186*J +0.0821*K -0.027*L -42.5949*M</t>
+  </si>
+  <si>
+    <t>-192.3596</t>
+  </si>
+  <si>
+    <t>0.0268</t>
+  </si>
+  <si>
+    <t>0.1173</t>
+  </si>
+  <si>
+    <t>0.0146</t>
+  </si>
+  <si>
+    <t>0.4673</t>
+  </si>
+  <si>
+    <t>0.0909</t>
+  </si>
+  <si>
+    <t>0.0186</t>
+  </si>
+  <si>
+    <t>0.0821</t>
+  </si>
+  <si>
+    <t>-0.0270</t>
+  </si>
+  <si>
+    <t>-42.5949</t>
+  </si>
+  <si>
+    <t>-281.3715 +0.0171*B + 0.0*C +0.3261*D -0.0426*E +0.1608*F + 0.0*G +0.1772*H +0.0178*I +0.0012*J -0.1989*K +1.326*L -8.9906*M</t>
+  </si>
+  <si>
+    <t>-281.3715</t>
+  </si>
+  <si>
+    <t>0.3261</t>
+  </si>
+  <si>
+    <t>-0.0426</t>
+  </si>
+  <si>
+    <t>0.1608</t>
+  </si>
+  <si>
+    <t>0.1772</t>
+  </si>
+  <si>
+    <t>0.0178</t>
+  </si>
+  <si>
+    <t>0.0012</t>
+  </si>
+  <si>
+    <t>-0.1989</t>
+  </si>
+  <si>
+    <t>1.3260</t>
+  </si>
+  <si>
+    <t>-8.9906</t>
+  </si>
+  <si>
+    <t>-721.9895 +0.0011*B + 0.0*C -0.1607*D +0.0444*E +0.0481*F + 0.0*G -0.4427*H +0.0236*I +0.0067*J -0.289*K +0.4363*L -18.6095*M</t>
+  </si>
+  <si>
+    <t>-721.9895</t>
+  </si>
+  <si>
+    <t>-0.1607</t>
+  </si>
+  <si>
+    <t>0.0444</t>
+  </si>
+  <si>
+    <t>-0.4427</t>
+  </si>
+  <si>
+    <t>0.0236</t>
+  </si>
+  <si>
+    <t>0.0067</t>
+  </si>
+  <si>
+    <t>-0.2890</t>
+  </si>
+  <si>
+    <t>0.4363</t>
+  </si>
+  <si>
+    <t>-18.6095</t>
+  </si>
+  <si>
+    <t>29.7375 +0.0431*B + 0.0*C +0.3371*D -0.0058*E -0.0053*F + 0.0*G +1.4359*H +0.0332*I +0.0088*J -0.0578*K +0.6922*L -15.8725*M</t>
+  </si>
+  <si>
+    <t>29.7375</t>
+  </si>
+  <si>
+    <t>0.3371</t>
+  </si>
+  <si>
+    <t>-0.0053</t>
+  </si>
+  <si>
+    <t>1.4359</t>
+  </si>
+  <si>
+    <t>0.0088</t>
+  </si>
+  <si>
+    <t>-0.0578</t>
+  </si>
+  <si>
+    <t>0.6922</t>
+  </si>
+  <si>
+    <t>-15.8725</t>
+  </si>
+  <si>
+    <t>-450.8838 +0.0084*B + 0.0*C -0.0575*D -0.0128*E +0.0195*F + 0.0*G +0.299*H +0.0233*I +0.0198*J -0.285*K +1.5981*L +28.0864*M</t>
+  </si>
+  <si>
+    <t>-450.8838</t>
+  </si>
+  <si>
+    <t>0.0084</t>
+  </si>
+  <si>
+    <t>-0.0575</t>
+  </si>
+  <si>
+    <t>-0.0128</t>
+  </si>
+  <si>
+    <t>0.2990</t>
+  </si>
+  <si>
+    <t>0.0233</t>
+  </si>
+  <si>
+    <t>-0.2850</t>
+  </si>
+  <si>
+    <t>1.5981</t>
+  </si>
+  <si>
+    <t>28.0864</t>
+  </si>
+  <si>
+    <t>-1018.5028 +0.0113*B + 0.0*C -0.1728*D -0.0352*E +0.0154*F + 0.0*G -0.2618*H +0.0868*I +0.0156*J +0.0543*K +1.2231*L -47.0035*M</t>
+  </si>
+  <si>
+    <t>-1018.5028</t>
+  </si>
+  <si>
+    <t>0.0113</t>
+  </si>
+  <si>
+    <t>-0.1728</t>
+  </si>
+  <si>
+    <t>-0.0352</t>
+  </si>
+  <si>
+    <t>0.0154</t>
+  </si>
+  <si>
+    <t>-0.2618</t>
+  </si>
+  <si>
+    <t>0.0868</t>
+  </si>
+  <si>
+    <t>0.0156</t>
+  </si>
+  <si>
+    <t>0.0543</t>
+  </si>
+  <si>
+    <t>1.2231</t>
+  </si>
+  <si>
+    <t>-47.0035</t>
+  </si>
+  <si>
+    <t>-432.2846 +0.0234*B + 0.0*C -0.4624*D +0.0196*E +0.0493*F + 0.0*G +0.0773*H +0.0538*I +0.012*J -0.087*K +1.6668*L -45.4864*M</t>
+  </si>
+  <si>
+    <t>-432.2846</t>
+  </si>
+  <si>
+    <t>0.0234</t>
+  </si>
+  <si>
+    <t>-0.4624</t>
+  </si>
+  <si>
+    <t>0.0773</t>
+  </si>
+  <si>
+    <t>0.0538</t>
+  </si>
+  <si>
+    <t>0.0120</t>
+  </si>
+  <si>
+    <t>-0.0870</t>
+  </si>
+  <si>
+    <t>1.6668</t>
+  </si>
+  <si>
+    <t>-45.4864</t>
+  </si>
+  <si>
+    <t>-0.6435 +0.0249*B + 0.0*C -0.1517*D +0.0096*E -0.009*F + 0.0*G +0.6758*H +0.0255*I +0.0049*J +0.035*K -0.2229*L -55.837*M</t>
+  </si>
+  <si>
+    <t>-0.6435</t>
+  </si>
+  <si>
+    <t>0.0249</t>
+  </si>
+  <si>
+    <t>-0.1517</t>
+  </si>
+  <si>
+    <t>0.0096</t>
+  </si>
+  <si>
+    <t>0.6758</t>
+  </si>
+  <si>
+    <t>0.0049</t>
+  </si>
+  <si>
+    <t>0.0350</t>
+  </si>
+  <si>
+    <t>-0.2229</t>
+  </si>
+  <si>
+    <t>-55.8370</t>
+  </si>
+  <si>
+    <t>-822.9184 +0.0251*B + 0.0*C -0.4822*D +0.0466*E -0.009*F + 0.0*G +1.0318*H +0.038*I +0.008*J -0.1029*K +0.896*L -12.4984*M</t>
+  </si>
+  <si>
+    <t>-822.9184</t>
+  </si>
+  <si>
+    <t>0.0251</t>
+  </si>
+  <si>
+    <t>-0.4822</t>
+  </si>
+  <si>
+    <t>1.0318</t>
+  </si>
+  <si>
+    <t>0.0380</t>
+  </si>
+  <si>
+    <t>0.0080</t>
+  </si>
+  <si>
+    <t>-0.1029</t>
+  </si>
+  <si>
+    <t>0.8960</t>
+  </si>
+  <si>
+    <t>-12.4984</t>
+  </si>
+  <si>
+    <t>168.6442 +0.018*B + 0.0*C +0.0048*D -0.0082*E +0.0608*F + 0.0*G +0.3918*H -0.0228*I +0.0006*J +0.0086*K +0.6646*L -17.1252*M</t>
+  </si>
+  <si>
+    <t>-0.0082</t>
+  </si>
+  <si>
+    <t>0.0608</t>
+  </si>
+  <si>
+    <t>0.3918</t>
+  </si>
+  <si>
+    <t>-0.0228</t>
+  </si>
+  <si>
+    <t>0.0086</t>
+  </si>
+  <si>
+    <t>0.6646</t>
+  </si>
+  <si>
+    <t>-17.1252</t>
+  </si>
+  <si>
+    <t>-226.7866 +0.0213*B + 0.0*C -0.2301*D -0.0189*E +0.0768*F + 0.0*G -0.2009*H +0.0443*I +0.0006*J +0.0333*K +0.9705*L -3.2142*M</t>
+  </si>
+  <si>
+    <t>-226.7866</t>
+  </si>
+  <si>
+    <t>-0.2301</t>
+  </si>
+  <si>
+    <t>-0.0189</t>
+  </si>
+  <si>
+    <t>0.0768</t>
+  </si>
+  <si>
+    <t>-0.2009</t>
+  </si>
+  <si>
+    <t>0.0443</t>
+  </si>
+  <si>
+    <t>0.9705</t>
+  </si>
+  <si>
+    <t>-3.2142</t>
+  </si>
+  <si>
+    <t>138.1666 +0.0404*B + 0.0*C +0.2989*D -0.0464*E -0.009*F + 0.0*G -0.0379*H +0.0322*I +0.0125*J -0.1185*K +0.6807*L -35.19*M</t>
+  </si>
+  <si>
+    <t>138.1666</t>
+  </si>
+  <si>
+    <t>0.0404</t>
+  </si>
+  <si>
+    <t>0.2989</t>
+  </si>
+  <si>
+    <t>-0.0464</t>
+  </si>
+  <si>
+    <t>-0.0379</t>
+  </si>
+  <si>
+    <t>0.0125</t>
+  </si>
+  <si>
+    <t>-0.1185</t>
+  </si>
+  <si>
+    <t>0.6807</t>
+  </si>
+  <si>
+    <t>-35.1900</t>
+  </si>
+  <si>
+    <t>-465.2115 +0.0011*B + 0.0*C -0.3606*D -0.0337*E +0.0029*F + 0.0*G +0.7356*H +0.0013*I +0.0281*J -0.0131*K +0.6787*L -38.4455*M</t>
+  </si>
+  <si>
+    <t>-465.2115</t>
+  </si>
+  <si>
+    <t>-0.3606</t>
+  </si>
+  <si>
+    <t>0.0029</t>
+  </si>
+  <si>
+    <t>-0.0131</t>
+  </si>
+  <si>
+    <t>0.6787</t>
+  </si>
+  <si>
+    <t>-38.4455</t>
+  </si>
+  <si>
+    <t>31.2906 +0.008*B + 0.0*C -0.0049*D +0.0674*E +0.0584*F + 0.0*G +0.7796*H +0.0091*I +0.0084*J +0.0974*K -0.1444*L +45.992*M</t>
+  </si>
+  <si>
+    <t>31.2906</t>
+  </si>
+  <si>
+    <t>-0.0049</t>
+  </si>
+  <si>
+    <t>0.0674</t>
+  </si>
+  <si>
+    <t>0.0584</t>
+  </si>
+  <si>
+    <t>0.7796</t>
+  </si>
+  <si>
+    <t>0.0974</t>
+  </si>
+  <si>
+    <t>-0.1444</t>
+  </si>
+  <si>
+    <t>45.9920</t>
+  </si>
+  <si>
+    <t>34.1073 +0.0082*B + 0.0*C +0.1689*D +0.0263*E +0.1036*F + 0.0*G -0.4736*H +0.0083*I +0.0069*J -0.0622*K +1.1207*L -5.6905*M</t>
+  </si>
+  <si>
+    <t>34.1073</t>
+  </si>
+  <si>
+    <t>0.1689</t>
+  </si>
+  <si>
+    <t>0.1036</t>
+  </si>
+  <si>
+    <t>-0.4736</t>
+  </si>
+  <si>
+    <t>0.0083</t>
+  </si>
+  <si>
+    <t>-0.0622</t>
+  </si>
+  <si>
+    <t>1.1207</t>
+  </si>
+  <si>
+    <t>-5.6905</t>
+  </si>
+  <si>
+    <t>-739.1663 +0.0218*B + 0.0*C +0.1614*D +0.0157*E +0.1325*F + 0.0*G +0.6343*H +0.0459*I +0.0082*J -0.1994*K +0.9269*L -4.7425*M</t>
+  </si>
+  <si>
+    <t>-739.1663</t>
+  </si>
+  <si>
+    <t>0.0218</t>
+  </si>
+  <si>
+    <t>0.1614</t>
+  </si>
+  <si>
+    <t>0.6343</t>
+  </si>
+  <si>
+    <t>0.0459</t>
+  </si>
+  <si>
+    <t>-0.1994</t>
+  </si>
+  <si>
+    <t>0.9269</t>
+  </si>
+  <si>
+    <t>-4.7425</t>
+  </si>
+  <si>
+    <t>-130.976 +0.0011*B + 0.0*C -0.4143*D +0.0284*E +0.0619*F + 0.0*G +0.5641*H +0.0322*I +0.0089*J +0.0254*K -0.0319*L -8.2697*M</t>
+  </si>
+  <si>
+    <t>-130.9760</t>
+  </si>
+  <si>
+    <t>-0.4143</t>
+  </si>
+  <si>
+    <t>0.0619</t>
+  </si>
+  <si>
+    <t>0.5641</t>
+  </si>
+  <si>
+    <t>0.0254</t>
+  </si>
+  <si>
+    <t>-0.0319</t>
+  </si>
+  <si>
+    <t>-8.2697</t>
+  </si>
+  <si>
+    <t>-408.726 +0.01*B + 0.0*C -0.1516*D +0.0069*E +0.0343*F + 0.0*G +0.8287*H +0.003*I +0.0073*J -0.0938*K +1.9585*L -5.0945*M</t>
+  </si>
+  <si>
+    <t>-408.7260</t>
+  </si>
+  <si>
+    <t>0.0343</t>
+  </si>
+  <si>
+    <t>0.8287</t>
+  </si>
+  <si>
+    <t>-0.0938</t>
+  </si>
+  <si>
+    <t>1.9585</t>
+  </si>
+  <si>
+    <t>-5.0945</t>
+  </si>
+  <si>
+    <t>156.7703 +0.0011*B + 0.0*C +0.0445*D +0.0242*E +0.0696*F + 0.0*G +0.741*H +0.015*I +0.0191*J +0.1431*K +0.1234*L -25.3931*M</t>
+  </si>
+  <si>
+    <t>156.7703</t>
+  </si>
+  <si>
+    <t>0.0242</t>
+  </si>
+  <si>
+    <t>0.0696</t>
+  </si>
+  <si>
+    <t>0.7410</t>
+  </si>
+  <si>
+    <t>0.0150</t>
+  </si>
+  <si>
+    <t>0.0191</t>
+  </si>
+  <si>
+    <t>0.1234</t>
+  </si>
+  <si>
+    <t>-25.3931</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0392*B + 0.0*C -0.2244*D -0.0097*E +0.0467*F + 0.0*G -0.3696*H +0.0022*I +0.0013*J -0.1221*K +0.4561*L -3.9039*M</t>
+  </si>
+  <si>
+    <t>0.0392</t>
+  </si>
+  <si>
+    <t>-0.2244</t>
+  </si>
+  <si>
+    <t>-0.0097</t>
+  </si>
+  <si>
+    <t>0.0467</t>
+  </si>
+  <si>
+    <t>-0.3696</t>
+  </si>
+  <si>
+    <t>-0.1221</t>
+  </si>
+  <si>
+    <t>0.4561</t>
+  </si>
+  <si>
+    <t>-3.9039</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0018*B + 0.0*C +0.2887*D -0.0043*E +0.0613*F + 0.0*G +0.561*H -0.0042*I +0.0115*J -0.0413*K +0.9906*L -2.1665*M</t>
+  </si>
+  <si>
+    <t>0.2887</t>
+  </si>
+  <si>
+    <t>0.0613</t>
+  </si>
+  <si>
+    <t>0.5610</t>
+  </si>
+  <si>
+    <t>0.0115</t>
+  </si>
+  <si>
+    <t>-0.0413</t>
+  </si>
+  <si>
+    <t>0.9906</t>
+  </si>
+  <si>
+    <t>-2.1665</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0071*B + 0.0*C -0.2271*D -0.0149*E +0.0294*F + 0.0*G -0.0437*H +0.069*I +0.0192*J -0.1051*K -0.3527*L +3.5952*M</t>
+  </si>
+  <si>
+    <t>0.0071</t>
+  </si>
+  <si>
+    <t>-0.2271</t>
+  </si>
+  <si>
+    <t>0.0294</t>
+  </si>
+  <si>
+    <t>-0.0437</t>
+  </si>
+  <si>
+    <t>0.0690</t>
+  </si>
+  <si>
+    <t>-0.1051</t>
+  </si>
+  <si>
+    <t>-0.3527</t>
+  </si>
+  <si>
+    <t>3.5952</t>
+  </si>
+  <si>
+    <t>-442.7696 +0.0255*B + 0.0*C +0.0227*D -0.038*E +0.1619*F + 0.0*G +1.0776*H +0.0119*I +0.0058*J -0.031*K +0.8304*L +9.5113*M</t>
+  </si>
+  <si>
+    <t>-442.7696</t>
+  </si>
+  <si>
+    <t>0.0227</t>
+  </si>
+  <si>
+    <t>-0.0380</t>
+  </si>
+  <si>
+    <t>0.1619</t>
+  </si>
+  <si>
+    <t>1.0776</t>
+  </si>
+  <si>
+    <t>0.0119</t>
+  </si>
+  <si>
+    <t>0.0058</t>
+  </si>
+  <si>
+    <t>-0.0310</t>
+  </si>
+  <si>
+    <t>0.8304</t>
+  </si>
+  <si>
+    <t>9.5113</t>
+  </si>
+  <si>
+    <t>168.6442 +0.0137*B + 0.0*C -0.3181*D -0.0345*E +0.0184*F + 0.0*G +0.2347*H +0.0882*I +0.0049*J -0.0364*K +0.4747*L +26.2625*M</t>
+  </si>
+  <si>
+    <t>0.0137</t>
+  </si>
+  <si>
+    <t>-0.3181</t>
+  </si>
+  <si>
+    <t>-0.0345</t>
+  </si>
+  <si>
+    <t>0.0184</t>
+  </si>
+  <si>
+    <t>0.2347</t>
+  </si>
+  <si>
+    <t>0.0882</t>
+  </si>
+  <si>
+    <t>-0.0364</t>
+  </si>
+  <si>
+    <t>0.4747</t>
+  </si>
+  <si>
+    <t>26.2625</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>65</t>
+  </si>
+  <si>
+    <t>66</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>68</t>
+  </si>
+  <si>
+    <t>69</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>74</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>76</t>
+  </si>
+  <si>
+    <t>77</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>79</t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>81</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>84</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>86</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>88</t>
+  </si>
+  <si>
+    <t>89</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>120</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -1480,14 +4043,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{1D7BFC85-1F6D-4A87-A64F-D6C4C591C01B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1789,7 +4354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr defaultRowHeight="14.6"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -3719,8 +6284,3768 @@
         <v>474</v>
       </c>
     </row>
+    <row r="42" spans="1:15">
+      <c r="A42" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B42" t="s">
+        <v>475</v>
+      </c>
+      <c r="C42" t="s">
+        <v>476</v>
+      </c>
+      <c r="D42" t="s">
+        <v>477</v>
+      </c>
+      <c r="E42" t="s">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s">
+        <v>478</v>
+      </c>
+      <c r="G42" t="s">
+        <v>479</v>
+      </c>
+      <c r="H42" t="s">
+        <v>480</v>
+      </c>
+      <c r="I42" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" t="s">
+        <v>481</v>
+      </c>
+      <c r="K42" t="s">
+        <v>482</v>
+      </c>
+      <c r="L42" t="s">
+        <v>477</v>
+      </c>
+      <c r="M42" t="s">
+        <v>483</v>
+      </c>
+      <c r="N42" t="s">
+        <v>484</v>
+      </c>
+      <c r="O42" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B43" t="s">
+        <v>486</v>
+      </c>
+      <c r="C43" t="s">
+        <v>487</v>
+      </c>
+      <c r="D43" t="s">
+        <v>488</v>
+      </c>
+      <c r="E43" t="s">
+        <v>19</v>
+      </c>
+      <c r="F43" t="s">
+        <v>489</v>
+      </c>
+      <c r="G43" t="s">
+        <v>490</v>
+      </c>
+      <c r="H43" t="s">
+        <v>491</v>
+      </c>
+      <c r="I43" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" t="s">
+        <v>492</v>
+      </c>
+      <c r="K43" t="s">
+        <v>493</v>
+      </c>
+      <c r="L43" t="s">
+        <v>494</v>
+      </c>
+      <c r="M43" t="s">
+        <v>495</v>
+      </c>
+      <c r="N43" t="s">
+        <v>496</v>
+      </c>
+      <c r="O43" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B44" t="s">
+        <v>498</v>
+      </c>
+      <c r="C44" t="s">
+        <v>499</v>
+      </c>
+      <c r="D44" t="s">
+        <v>500</v>
+      </c>
+      <c r="E44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F44" t="s">
+        <v>501</v>
+      </c>
+      <c r="G44" t="s">
+        <v>94</v>
+      </c>
+      <c r="H44" t="s">
+        <v>502</v>
+      </c>
+      <c r="I44" t="s">
+        <v>19</v>
+      </c>
+      <c r="J44" t="s">
+        <v>503</v>
+      </c>
+      <c r="K44" t="s">
+        <v>504</v>
+      </c>
+      <c r="L44" t="s">
+        <v>505</v>
+      </c>
+      <c r="M44" t="s">
+        <v>506</v>
+      </c>
+      <c r="N44" t="s">
+        <v>507</v>
+      </c>
+      <c r="O44" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B45" t="s">
+        <v>509</v>
+      </c>
+      <c r="C45" t="s">
+        <v>510</v>
+      </c>
+      <c r="D45" t="s">
+        <v>511</v>
+      </c>
+      <c r="E45" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" t="s">
+        <v>512</v>
+      </c>
+      <c r="G45" t="s">
+        <v>505</v>
+      </c>
+      <c r="H45" t="s">
+        <v>513</v>
+      </c>
+      <c r="I45" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" t="s">
+        <v>514</v>
+      </c>
+      <c r="K45" t="s">
+        <v>515</v>
+      </c>
+      <c r="L45" t="s">
+        <v>516</v>
+      </c>
+      <c r="M45" t="s">
+        <v>517</v>
+      </c>
+      <c r="N45" t="s">
+        <v>518</v>
+      </c>
+      <c r="O45" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B46" t="s">
+        <v>520</v>
+      </c>
+      <c r="C46" t="s">
+        <v>521</v>
+      </c>
+      <c r="D46" t="s">
+        <v>522</v>
+      </c>
+      <c r="E46" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" t="s">
+        <v>523</v>
+      </c>
+      <c r="G46" t="s">
+        <v>524</v>
+      </c>
+      <c r="H46" t="s">
+        <v>525</v>
+      </c>
+      <c r="I46" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" t="s">
+        <v>526</v>
+      </c>
+      <c r="K46" t="s">
+        <v>527</v>
+      </c>
+      <c r="L46" t="s">
+        <v>522</v>
+      </c>
+      <c r="M46" t="s">
+        <v>528</v>
+      </c>
+      <c r="N46" t="s">
+        <v>529</v>
+      </c>
+      <c r="O46" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B47" t="s">
+        <v>531</v>
+      </c>
+      <c r="C47" t="s">
+        <v>532</v>
+      </c>
+      <c r="D47" t="s">
+        <v>119</v>
+      </c>
+      <c r="E47" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" t="s">
+        <v>533</v>
+      </c>
+      <c r="G47" t="s">
+        <v>534</v>
+      </c>
+      <c r="H47" t="s">
+        <v>535</v>
+      </c>
+      <c r="I47" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" t="s">
+        <v>536</v>
+      </c>
+      <c r="K47" t="s">
+        <v>537</v>
+      </c>
+      <c r="L47" t="s">
+        <v>332</v>
+      </c>
+      <c r="M47" t="s">
+        <v>538</v>
+      </c>
+      <c r="N47" t="s">
+        <v>539</v>
+      </c>
+      <c r="O47" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B48" t="s">
+        <v>541</v>
+      </c>
+      <c r="C48" t="s">
+        <v>542</v>
+      </c>
+      <c r="D48" t="s">
+        <v>543</v>
+      </c>
+      <c r="E48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" t="s">
+        <v>544</v>
+      </c>
+      <c r="G48" t="s">
+        <v>545</v>
+      </c>
+      <c r="H48" t="s">
+        <v>546</v>
+      </c>
+      <c r="I48" t="s">
+        <v>19</v>
+      </c>
+      <c r="J48" t="s">
+        <v>547</v>
+      </c>
+      <c r="K48" t="s">
+        <v>548</v>
+      </c>
+      <c r="L48" t="s">
+        <v>158</v>
+      </c>
+      <c r="M48" t="s">
+        <v>549</v>
+      </c>
+      <c r="N48" t="s">
+        <v>550</v>
+      </c>
+      <c r="O48" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B49" t="s">
+        <v>552</v>
+      </c>
+      <c r="C49" t="s">
+        <v>553</v>
+      </c>
+      <c r="D49" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" t="s">
+        <v>554</v>
+      </c>
+      <c r="G49" t="s">
+        <v>297</v>
+      </c>
+      <c r="H49" t="s">
+        <v>555</v>
+      </c>
+      <c r="I49" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" t="s">
+        <v>556</v>
+      </c>
+      <c r="K49" t="s">
+        <v>557</v>
+      </c>
+      <c r="L49" t="s">
+        <v>558</v>
+      </c>
+      <c r="M49" t="s">
+        <v>559</v>
+      </c>
+      <c r="N49" t="s">
+        <v>560</v>
+      </c>
+      <c r="O49" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B50" t="s">
+        <v>562</v>
+      </c>
+      <c r="C50" t="s">
+        <v>563</v>
+      </c>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E50" t="s">
+        <v>19</v>
+      </c>
+      <c r="F50" t="s">
+        <v>564</v>
+      </c>
+      <c r="G50" t="s">
+        <v>565</v>
+      </c>
+      <c r="H50" t="s">
+        <v>158</v>
+      </c>
+      <c r="I50" t="s">
+        <v>19</v>
+      </c>
+      <c r="J50" t="s">
+        <v>566</v>
+      </c>
+      <c r="K50" t="s">
+        <v>567</v>
+      </c>
+      <c r="L50" t="s">
+        <v>332</v>
+      </c>
+      <c r="M50" t="s">
+        <v>568</v>
+      </c>
+      <c r="N50" t="s">
+        <v>569</v>
+      </c>
+      <c r="O50" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B51" t="s">
+        <v>571</v>
+      </c>
+      <c r="C51" t="s">
+        <v>572</v>
+      </c>
+      <c r="D51" t="s">
+        <v>500</v>
+      </c>
+      <c r="E51" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" t="s">
+        <v>573</v>
+      </c>
+      <c r="G51" t="s">
+        <v>162</v>
+      </c>
+      <c r="H51" t="s">
+        <v>574</v>
+      </c>
+      <c r="I51" t="s">
+        <v>19</v>
+      </c>
+      <c r="J51" t="s">
+        <v>575</v>
+      </c>
+      <c r="K51" t="s">
+        <v>576</v>
+      </c>
+      <c r="L51" t="s">
+        <v>459</v>
+      </c>
+      <c r="M51" t="s">
+        <v>577</v>
+      </c>
+      <c r="N51" t="s">
+        <v>578</v>
+      </c>
+      <c r="O51" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B52" t="s">
+        <v>580</v>
+      </c>
+      <c r="C52" t="s">
+        <v>581</v>
+      </c>
+      <c r="D52" t="s">
+        <v>582</v>
+      </c>
+      <c r="E52" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" t="s">
+        <v>583</v>
+      </c>
+      <c r="G52" t="s">
+        <v>584</v>
+      </c>
+      <c r="H52" t="s">
+        <v>585</v>
+      </c>
+      <c r="I52" t="s">
+        <v>19</v>
+      </c>
+      <c r="J52" t="s">
+        <v>586</v>
+      </c>
+      <c r="K52" t="s">
+        <v>548</v>
+      </c>
+      <c r="L52" t="s">
+        <v>332</v>
+      </c>
+      <c r="M52" t="s">
+        <v>587</v>
+      </c>
+      <c r="N52" t="s">
+        <v>588</v>
+      </c>
+      <c r="O52" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B53" t="s">
+        <v>590</v>
+      </c>
+      <c r="C53" t="s">
+        <v>591</v>
+      </c>
+      <c r="D53" t="s">
+        <v>592</v>
+      </c>
+      <c r="E53" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" t="s">
+        <v>593</v>
+      </c>
+      <c r="G53" t="s">
+        <v>594</v>
+      </c>
+      <c r="H53" t="s">
+        <v>595</v>
+      </c>
+      <c r="I53" t="s">
+        <v>19</v>
+      </c>
+      <c r="J53" t="s">
+        <v>596</v>
+      </c>
+      <c r="K53" t="s">
+        <v>597</v>
+      </c>
+      <c r="L53" t="s">
+        <v>450</v>
+      </c>
+      <c r="M53" t="s">
+        <v>598</v>
+      </c>
+      <c r="N53" t="s">
+        <v>599</v>
+      </c>
+      <c r="O53" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B54" t="s">
+        <v>601</v>
+      </c>
+      <c r="C54" t="s">
+        <v>602</v>
+      </c>
+      <c r="D54" t="s">
+        <v>264</v>
+      </c>
+      <c r="E54" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" t="s">
+        <v>603</v>
+      </c>
+      <c r="G54" t="s">
+        <v>493</v>
+      </c>
+      <c r="H54" t="s">
+        <v>604</v>
+      </c>
+      <c r="I54" t="s">
+        <v>19</v>
+      </c>
+      <c r="J54" t="s">
+        <v>605</v>
+      </c>
+      <c r="K54" t="s">
+        <v>606</v>
+      </c>
+      <c r="L54" t="s">
+        <v>332</v>
+      </c>
+      <c r="M54" t="s">
+        <v>607</v>
+      </c>
+      <c r="N54" t="s">
+        <v>608</v>
+      </c>
+      <c r="O54" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B55" t="s">
+        <v>610</v>
+      </c>
+      <c r="C55" t="s">
+        <v>611</v>
+      </c>
+      <c r="D55" t="s">
+        <v>612</v>
+      </c>
+      <c r="E55" t="s">
+        <v>19</v>
+      </c>
+      <c r="F55" t="s">
+        <v>613</v>
+      </c>
+      <c r="G55" t="s">
+        <v>614</v>
+      </c>
+      <c r="H55" t="s">
+        <v>513</v>
+      </c>
+      <c r="I55" t="s">
+        <v>19</v>
+      </c>
+      <c r="J55" t="s">
+        <v>615</v>
+      </c>
+      <c r="K55" t="s">
+        <v>74</v>
+      </c>
+      <c r="L55" t="s">
+        <v>616</v>
+      </c>
+      <c r="M55" t="s">
+        <v>617</v>
+      </c>
+      <c r="N55" t="s">
+        <v>618</v>
+      </c>
+      <c r="O55" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B56" t="s">
+        <v>620</v>
+      </c>
+      <c r="C56" t="s">
+        <v>621</v>
+      </c>
+      <c r="D56" t="s">
+        <v>622</v>
+      </c>
+      <c r="E56" t="s">
+        <v>19</v>
+      </c>
+      <c r="F56" t="s">
+        <v>623</v>
+      </c>
+      <c r="G56" t="s">
+        <v>624</v>
+      </c>
+      <c r="H56" t="s">
+        <v>513</v>
+      </c>
+      <c r="I56" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" t="s">
+        <v>625</v>
+      </c>
+      <c r="K56" t="s">
+        <v>382</v>
+      </c>
+      <c r="L56" t="s">
+        <v>626</v>
+      </c>
+      <c r="M56" t="s">
+        <v>627</v>
+      </c>
+      <c r="N56" t="s">
+        <v>628</v>
+      </c>
+      <c r="O56" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B57" t="s">
+        <v>630</v>
+      </c>
+      <c r="C57" t="s">
+        <v>631</v>
+      </c>
+      <c r="D57" t="s">
+        <v>511</v>
+      </c>
+      <c r="E57" t="s">
+        <v>19</v>
+      </c>
+      <c r="F57" t="s">
+        <v>632</v>
+      </c>
+      <c r="G57" t="s">
+        <v>633</v>
+      </c>
+      <c r="H57" t="s">
+        <v>51</v>
+      </c>
+      <c r="I57" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" t="s">
+        <v>634</v>
+      </c>
+      <c r="K57" t="s">
+        <v>320</v>
+      </c>
+      <c r="L57" t="s">
+        <v>314</v>
+      </c>
+      <c r="M57" t="s">
+        <v>635</v>
+      </c>
+      <c r="N57" t="s">
+        <v>636</v>
+      </c>
+      <c r="O57" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B58" t="s">
+        <v>638</v>
+      </c>
+      <c r="C58" t="s">
+        <v>639</v>
+      </c>
+      <c r="D58" t="s">
+        <v>640</v>
+      </c>
+      <c r="E58" t="s">
+        <v>19</v>
+      </c>
+      <c r="F58" t="s">
+        <v>641</v>
+      </c>
+      <c r="G58" t="s">
+        <v>305</v>
+      </c>
+      <c r="H58" t="s">
+        <v>642</v>
+      </c>
+      <c r="I58" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" t="s">
+        <v>643</v>
+      </c>
+      <c r="K58" t="s">
+        <v>644</v>
+      </c>
+      <c r="L58" t="s">
+        <v>645</v>
+      </c>
+      <c r="M58" t="s">
+        <v>646</v>
+      </c>
+      <c r="N58" t="s">
+        <v>647</v>
+      </c>
+      <c r="O58" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B59" t="s">
+        <v>649</v>
+      </c>
+      <c r="C59" t="s">
+        <v>650</v>
+      </c>
+      <c r="D59" t="s">
+        <v>651</v>
+      </c>
+      <c r="E59" t="s">
+        <v>19</v>
+      </c>
+      <c r="F59" t="s">
+        <v>652</v>
+      </c>
+      <c r="G59" t="s">
+        <v>653</v>
+      </c>
+      <c r="H59" t="s">
+        <v>654</v>
+      </c>
+      <c r="I59" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" t="s">
+        <v>655</v>
+      </c>
+      <c r="K59" t="s">
+        <v>502</v>
+      </c>
+      <c r="L59" t="s">
+        <v>656</v>
+      </c>
+      <c r="M59" t="s">
+        <v>657</v>
+      </c>
+      <c r="N59" t="s">
+        <v>658</v>
+      </c>
+      <c r="O59" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B60" t="s">
+        <v>660</v>
+      </c>
+      <c r="C60" t="s">
+        <v>661</v>
+      </c>
+      <c r="D60" t="s">
+        <v>500</v>
+      </c>
+      <c r="E60" t="s">
+        <v>19</v>
+      </c>
+      <c r="F60" t="s">
+        <v>662</v>
+      </c>
+      <c r="G60" t="s">
+        <v>663</v>
+      </c>
+      <c r="H60" t="s">
+        <v>664</v>
+      </c>
+      <c r="I60" t="s">
+        <v>19</v>
+      </c>
+      <c r="J60" t="s">
+        <v>665</v>
+      </c>
+      <c r="K60" t="s">
+        <v>666</v>
+      </c>
+      <c r="L60" t="s">
+        <v>401</v>
+      </c>
+      <c r="M60" t="s">
+        <v>667</v>
+      </c>
+      <c r="N60" t="s">
+        <v>668</v>
+      </c>
+      <c r="O60" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B61" t="s">
+        <v>670</v>
+      </c>
+      <c r="C61" t="s">
+        <v>671</v>
+      </c>
+      <c r="D61" t="s">
+        <v>672</v>
+      </c>
+      <c r="E61" t="s">
+        <v>19</v>
+      </c>
+      <c r="F61" t="s">
+        <v>673</v>
+      </c>
+      <c r="G61" t="s">
+        <v>674</v>
+      </c>
+      <c r="H61" t="s">
+        <v>675</v>
+      </c>
+      <c r="I61" t="s">
+        <v>19</v>
+      </c>
+      <c r="J61" t="s">
+        <v>676</v>
+      </c>
+      <c r="K61" t="s">
+        <v>677</v>
+      </c>
+      <c r="L61" t="s">
+        <v>678</v>
+      </c>
+      <c r="M61" t="s">
+        <v>679</v>
+      </c>
+      <c r="N61" t="s">
+        <v>680</v>
+      </c>
+      <c r="O61" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B62" t="s">
+        <v>682</v>
+      </c>
+      <c r="C62" t="s">
+        <v>671</v>
+      </c>
+      <c r="D62" t="s">
+        <v>500</v>
+      </c>
+      <c r="E62" t="s">
+        <v>19</v>
+      </c>
+      <c r="F62" t="s">
+        <v>683</v>
+      </c>
+      <c r="G62" t="s">
+        <v>684</v>
+      </c>
+      <c r="H62" t="s">
+        <v>317</v>
+      </c>
+      <c r="I62" t="s">
+        <v>19</v>
+      </c>
+      <c r="J62" t="s">
+        <v>685</v>
+      </c>
+      <c r="K62" t="s">
+        <v>686</v>
+      </c>
+      <c r="L62" t="s">
+        <v>391</v>
+      </c>
+      <c r="M62" t="s">
+        <v>687</v>
+      </c>
+      <c r="N62" t="s">
+        <v>688</v>
+      </c>
+      <c r="O62" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B63" t="s">
+        <v>690</v>
+      </c>
+      <c r="C63" t="s">
+        <v>691</v>
+      </c>
+      <c r="D63" t="s">
+        <v>692</v>
+      </c>
+      <c r="E63" t="s">
+        <v>19</v>
+      </c>
+      <c r="F63" t="s">
+        <v>693</v>
+      </c>
+      <c r="G63" t="s">
+        <v>694</v>
+      </c>
+      <c r="H63" t="s">
+        <v>695</v>
+      </c>
+      <c r="I63" t="s">
+        <v>19</v>
+      </c>
+      <c r="J63" t="s">
+        <v>696</v>
+      </c>
+      <c r="K63" t="s">
+        <v>697</v>
+      </c>
+      <c r="L63" t="s">
+        <v>407</v>
+      </c>
+      <c r="M63" t="s">
+        <v>698</v>
+      </c>
+      <c r="N63" t="s">
+        <v>699</v>
+      </c>
+      <c r="O63" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B64" t="s">
+        <v>701</v>
+      </c>
+      <c r="C64" t="s">
+        <v>702</v>
+      </c>
+      <c r="D64" t="s">
+        <v>703</v>
+      </c>
+      <c r="E64" t="s">
+        <v>19</v>
+      </c>
+      <c r="F64" t="s">
+        <v>704</v>
+      </c>
+      <c r="G64" t="s">
+        <v>705</v>
+      </c>
+      <c r="H64" t="s">
+        <v>706</v>
+      </c>
+      <c r="I64" t="s">
+        <v>19</v>
+      </c>
+      <c r="J64" t="s">
+        <v>707</v>
+      </c>
+      <c r="K64" t="s">
+        <v>546</v>
+      </c>
+      <c r="L64" t="s">
+        <v>190</v>
+      </c>
+      <c r="M64" t="s">
+        <v>708</v>
+      </c>
+      <c r="N64" t="s">
+        <v>709</v>
+      </c>
+      <c r="O64" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B65" t="s">
+        <v>711</v>
+      </c>
+      <c r="C65" t="s">
+        <v>712</v>
+      </c>
+      <c r="D65" t="s">
+        <v>500</v>
+      </c>
+      <c r="E65" t="s">
+        <v>19</v>
+      </c>
+      <c r="F65" t="s">
+        <v>713</v>
+      </c>
+      <c r="G65" t="s">
+        <v>714</v>
+      </c>
+      <c r="H65" t="s">
+        <v>488</v>
+      </c>
+      <c r="I65" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" t="s">
+        <v>715</v>
+      </c>
+      <c r="K65" t="s">
+        <v>716</v>
+      </c>
+      <c r="L65" t="s">
+        <v>717</v>
+      </c>
+      <c r="M65" t="s">
+        <v>718</v>
+      </c>
+      <c r="N65" t="s">
+        <v>719</v>
+      </c>
+      <c r="O65" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B66" t="s">
+        <v>721</v>
+      </c>
+      <c r="C66" t="s">
+        <v>722</v>
+      </c>
+      <c r="D66" t="s">
+        <v>500</v>
+      </c>
+      <c r="E66" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" t="s">
+        <v>723</v>
+      </c>
+      <c r="G66" t="s">
+        <v>724</v>
+      </c>
+      <c r="H66" t="s">
+        <v>725</v>
+      </c>
+      <c r="I66" t="s">
+        <v>19</v>
+      </c>
+      <c r="J66" t="s">
+        <v>726</v>
+      </c>
+      <c r="K66" t="s">
+        <v>727</v>
+      </c>
+      <c r="L66" t="s">
+        <v>332</v>
+      </c>
+      <c r="M66" t="s">
+        <v>728</v>
+      </c>
+      <c r="N66" t="s">
+        <v>729</v>
+      </c>
+      <c r="O66" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B67" t="s">
+        <v>731</v>
+      </c>
+      <c r="C67" t="s">
+        <v>732</v>
+      </c>
+      <c r="D67" t="s">
+        <v>733</v>
+      </c>
+      <c r="E67" t="s">
+        <v>19</v>
+      </c>
+      <c r="F67" t="s">
+        <v>734</v>
+      </c>
+      <c r="G67" t="s">
+        <v>678</v>
+      </c>
+      <c r="H67" t="s">
+        <v>735</v>
+      </c>
+      <c r="I67" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" t="s">
+        <v>736</v>
+      </c>
+      <c r="K67" t="s">
+        <v>585</v>
+      </c>
+      <c r="L67" t="s">
+        <v>737</v>
+      </c>
+      <c r="M67" t="s">
+        <v>738</v>
+      </c>
+      <c r="N67" t="s">
+        <v>739</v>
+      </c>
+      <c r="O67" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B68" t="s">
+        <v>741</v>
+      </c>
+      <c r="C68" t="s">
+        <v>742</v>
+      </c>
+      <c r="D68" t="s">
+        <v>142</v>
+      </c>
+      <c r="E68" t="s">
+        <v>19</v>
+      </c>
+      <c r="F68" t="s">
+        <v>743</v>
+      </c>
+      <c r="G68" t="s">
+        <v>744</v>
+      </c>
+      <c r="H68" t="s">
+        <v>745</v>
+      </c>
+      <c r="I68" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" t="s">
+        <v>434</v>
+      </c>
+      <c r="K68" t="s">
+        <v>746</v>
+      </c>
+      <c r="L68" t="s">
+        <v>557</v>
+      </c>
+      <c r="M68" t="s">
+        <v>747</v>
+      </c>
+      <c r="N68" t="s">
+        <v>748</v>
+      </c>
+      <c r="O68" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B69" t="s">
+        <v>750</v>
+      </c>
+      <c r="C69" t="s">
+        <v>751</v>
+      </c>
+      <c r="D69" t="s">
+        <v>752</v>
+      </c>
+      <c r="E69" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" t="s">
+        <v>753</v>
+      </c>
+      <c r="G69" t="s">
+        <v>754</v>
+      </c>
+      <c r="H69" t="s">
+        <v>446</v>
+      </c>
+      <c r="I69" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" t="s">
+        <v>755</v>
+      </c>
+      <c r="K69" t="s">
+        <v>756</v>
+      </c>
+      <c r="L69" t="s">
+        <v>389</v>
+      </c>
+      <c r="M69" t="s">
+        <v>757</v>
+      </c>
+      <c r="N69" t="s">
+        <v>758</v>
+      </c>
+      <c r="O69" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B70" t="s">
+        <v>760</v>
+      </c>
+      <c r="C70" t="s">
+        <v>761</v>
+      </c>
+      <c r="D70" t="s">
+        <v>597</v>
+      </c>
+      <c r="E70" t="s">
+        <v>19</v>
+      </c>
+      <c r="F70" t="s">
+        <v>762</v>
+      </c>
+      <c r="G70" t="s">
+        <v>763</v>
+      </c>
+      <c r="H70" t="s">
+        <v>764</v>
+      </c>
+      <c r="I70" t="s">
+        <v>19</v>
+      </c>
+      <c r="J70" t="s">
+        <v>765</v>
+      </c>
+      <c r="K70" t="s">
+        <v>260</v>
+      </c>
+      <c r="L70" t="s">
+        <v>766</v>
+      </c>
+      <c r="M70" t="s">
+        <v>155</v>
+      </c>
+      <c r="N70" t="s">
+        <v>767</v>
+      </c>
+      <c r="O70" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
+      <c r="A71" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B71" t="s">
+        <v>769</v>
+      </c>
+      <c r="C71" t="s">
+        <v>770</v>
+      </c>
+      <c r="D71" t="s">
+        <v>771</v>
+      </c>
+      <c r="E71" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" t="s">
+        <v>772</v>
+      </c>
+      <c r="G71" t="s">
+        <v>773</v>
+      </c>
+      <c r="H71" t="s">
+        <v>774</v>
+      </c>
+      <c r="I71" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" t="s">
+        <v>775</v>
+      </c>
+      <c r="K71" t="s">
+        <v>776</v>
+      </c>
+      <c r="L71" t="s">
+        <v>777</v>
+      </c>
+      <c r="M71" t="s">
+        <v>746</v>
+      </c>
+      <c r="N71" t="s">
+        <v>778</v>
+      </c>
+      <c r="O71" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
+      <c r="A72" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B72" t="s">
+        <v>780</v>
+      </c>
+      <c r="C72" t="s">
+        <v>781</v>
+      </c>
+      <c r="D72" t="s">
+        <v>155</v>
+      </c>
+      <c r="E72" t="s">
+        <v>19</v>
+      </c>
+      <c r="F72" t="s">
+        <v>782</v>
+      </c>
+      <c r="G72" t="s">
+        <v>783</v>
+      </c>
+      <c r="H72" t="s">
+        <v>535</v>
+      </c>
+      <c r="I72" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" t="s">
+        <v>784</v>
+      </c>
+      <c r="K72" t="s">
+        <v>458</v>
+      </c>
+      <c r="L72" t="s">
+        <v>371</v>
+      </c>
+      <c r="M72" t="s">
+        <v>773</v>
+      </c>
+      <c r="N72" t="s">
+        <v>785</v>
+      </c>
+      <c r="O72" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B73" t="s">
+        <v>787</v>
+      </c>
+      <c r="C73" t="s">
+        <v>788</v>
+      </c>
+      <c r="D73" t="s">
+        <v>789</v>
+      </c>
+      <c r="E73" t="s">
+        <v>19</v>
+      </c>
+      <c r="F73" t="s">
+        <v>790</v>
+      </c>
+      <c r="G73" t="s">
+        <v>791</v>
+      </c>
+      <c r="H73" t="s">
+        <v>792</v>
+      </c>
+      <c r="I73" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" t="s">
+        <v>793</v>
+      </c>
+      <c r="K73" t="s">
+        <v>794</v>
+      </c>
+      <c r="L73" t="s">
+        <v>795</v>
+      </c>
+      <c r="M73" t="s">
+        <v>796</v>
+      </c>
+      <c r="N73" t="s">
+        <v>797</v>
+      </c>
+      <c r="O73" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B74" t="s">
+        <v>799</v>
+      </c>
+      <c r="C74" t="s">
+        <v>800</v>
+      </c>
+      <c r="D74" t="s">
+        <v>801</v>
+      </c>
+      <c r="E74" t="s">
+        <v>19</v>
+      </c>
+      <c r="F74" t="s">
+        <v>802</v>
+      </c>
+      <c r="G74" t="s">
+        <v>803</v>
+      </c>
+      <c r="H74" t="s">
+        <v>804</v>
+      </c>
+      <c r="I74" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" t="s">
+        <v>805</v>
+      </c>
+      <c r="K74" t="s">
+        <v>527</v>
+      </c>
+      <c r="L74" t="s">
+        <v>107</v>
+      </c>
+      <c r="M74" t="s">
+        <v>806</v>
+      </c>
+      <c r="N74" t="s">
+        <v>807</v>
+      </c>
+      <c r="O74" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B75" t="s">
+        <v>809</v>
+      </c>
+      <c r="C75" t="s">
+        <v>810</v>
+      </c>
+      <c r="D75" t="s">
+        <v>811</v>
+      </c>
+      <c r="E75" t="s">
+        <v>19</v>
+      </c>
+      <c r="F75" t="s">
+        <v>812</v>
+      </c>
+      <c r="G75" t="s">
+        <v>813</v>
+      </c>
+      <c r="H75" t="s">
+        <v>814</v>
+      </c>
+      <c r="I75" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" t="s">
+        <v>815</v>
+      </c>
+      <c r="K75" t="s">
+        <v>816</v>
+      </c>
+      <c r="L75" t="s">
+        <v>766</v>
+      </c>
+      <c r="M75" t="s">
+        <v>817</v>
+      </c>
+      <c r="N75" t="s">
+        <v>818</v>
+      </c>
+      <c r="O75" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B76" t="s">
+        <v>820</v>
+      </c>
+      <c r="C76" t="s">
+        <v>671</v>
+      </c>
+      <c r="D76" t="s">
+        <v>458</v>
+      </c>
+      <c r="E76" t="s">
+        <v>19</v>
+      </c>
+      <c r="F76" t="s">
+        <v>821</v>
+      </c>
+      <c r="G76" t="s">
+        <v>522</v>
+      </c>
+      <c r="H76" t="s">
+        <v>595</v>
+      </c>
+      <c r="I76" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" t="s">
+        <v>822</v>
+      </c>
+      <c r="K76" t="s">
+        <v>433</v>
+      </c>
+      <c r="L76" t="s">
+        <v>331</v>
+      </c>
+      <c r="M76" t="s">
+        <v>823</v>
+      </c>
+      <c r="N76" t="s">
+        <v>824</v>
+      </c>
+      <c r="O76" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B77" t="s">
+        <v>826</v>
+      </c>
+      <c r="C77" t="s">
+        <v>827</v>
+      </c>
+      <c r="D77" t="s">
+        <v>828</v>
+      </c>
+      <c r="E77" t="s">
+        <v>19</v>
+      </c>
+      <c r="F77" t="s">
+        <v>829</v>
+      </c>
+      <c r="G77" t="s">
+        <v>830</v>
+      </c>
+      <c r="H77" t="s">
+        <v>752</v>
+      </c>
+      <c r="I77" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" t="s">
+        <v>831</v>
+      </c>
+      <c r="K77" t="s">
+        <v>832</v>
+      </c>
+      <c r="L77" t="s">
+        <v>332</v>
+      </c>
+      <c r="M77" t="s">
+        <v>833</v>
+      </c>
+      <c r="N77" t="s">
+        <v>834</v>
+      </c>
+      <c r="O77" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B78" t="s">
+        <v>836</v>
+      </c>
+      <c r="C78" t="s">
+        <v>837</v>
+      </c>
+      <c r="D78" t="s">
+        <v>838</v>
+      </c>
+      <c r="E78" t="s">
+        <v>19</v>
+      </c>
+      <c r="F78" t="s">
+        <v>839</v>
+      </c>
+      <c r="G78" t="s">
+        <v>840</v>
+      </c>
+      <c r="H78" t="s">
+        <v>513</v>
+      </c>
+      <c r="I78" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" t="s">
+        <v>635</v>
+      </c>
+      <c r="K78" t="s">
+        <v>841</v>
+      </c>
+      <c r="L78" t="s">
+        <v>842</v>
+      </c>
+      <c r="M78" t="s">
+        <v>843</v>
+      </c>
+      <c r="N78" t="s">
+        <v>844</v>
+      </c>
+      <c r="O78" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B79" t="s">
+        <v>846</v>
+      </c>
+      <c r="C79" t="s">
+        <v>847</v>
+      </c>
+      <c r="D79" t="s">
+        <v>848</v>
+      </c>
+      <c r="E79" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" t="s">
+        <v>849</v>
+      </c>
+      <c r="G79" t="s">
+        <v>850</v>
+      </c>
+      <c r="H79" t="s">
+        <v>851</v>
+      </c>
+      <c r="I79" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" t="s">
+        <v>852</v>
+      </c>
+      <c r="K79" t="s">
+        <v>853</v>
+      </c>
+      <c r="L79" t="s">
+        <v>854</v>
+      </c>
+      <c r="M79" t="s">
+        <v>762</v>
+      </c>
+      <c r="N79" t="s">
+        <v>855</v>
+      </c>
+      <c r="O79" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B80" t="s">
+        <v>857</v>
+      </c>
+      <c r="C80" t="s">
+        <v>671</v>
+      </c>
+      <c r="D80" t="s">
+        <v>858</v>
+      </c>
+      <c r="E80" t="s">
+        <v>19</v>
+      </c>
+      <c r="F80" t="s">
+        <v>859</v>
+      </c>
+      <c r="G80" t="s">
+        <v>860</v>
+      </c>
+      <c r="H80" t="s">
+        <v>370</v>
+      </c>
+      <c r="I80" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" t="s">
+        <v>861</v>
+      </c>
+      <c r="K80" t="s">
+        <v>862</v>
+      </c>
+      <c r="L80" t="s">
+        <v>863</v>
+      </c>
+      <c r="M80" t="s">
+        <v>864</v>
+      </c>
+      <c r="N80" t="s">
+        <v>865</v>
+      </c>
+      <c r="O80" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
+      <c r="A81" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B81" t="s">
+        <v>867</v>
+      </c>
+      <c r="C81" t="s">
+        <v>868</v>
+      </c>
+      <c r="D81" t="s">
+        <v>500</v>
+      </c>
+      <c r="E81" t="s">
+        <v>19</v>
+      </c>
+      <c r="F81" t="s">
+        <v>869</v>
+      </c>
+      <c r="G81" t="s">
+        <v>39</v>
+      </c>
+      <c r="H81" t="s">
+        <v>870</v>
+      </c>
+      <c r="I81" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" t="s">
+        <v>871</v>
+      </c>
+      <c r="K81" t="s">
+        <v>872</v>
+      </c>
+      <c r="L81" t="s">
+        <v>87</v>
+      </c>
+      <c r="M81" t="s">
+        <v>873</v>
+      </c>
+      <c r="N81" t="s">
+        <v>719</v>
+      </c>
+      <c r="O81" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
+      <c r="A82" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B82" t="s">
+        <v>875</v>
+      </c>
+      <c r="C82" t="s">
+        <v>876</v>
+      </c>
+      <c r="D82" t="s">
+        <v>877</v>
+      </c>
+      <c r="E82" t="s">
+        <v>19</v>
+      </c>
+      <c r="F82" t="s">
+        <v>878</v>
+      </c>
+      <c r="G82" t="s">
+        <v>63</v>
+      </c>
+      <c r="H82" t="s">
+        <v>513</v>
+      </c>
+      <c r="I82" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" t="s">
+        <v>879</v>
+      </c>
+      <c r="K82" t="s">
+        <v>880</v>
+      </c>
+      <c r="L82" t="s">
+        <v>401</v>
+      </c>
+      <c r="M82" t="s">
+        <v>881</v>
+      </c>
+      <c r="N82" t="s">
+        <v>882</v>
+      </c>
+      <c r="O82" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="83" spans="1:15">
+      <c r="A83" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B83" t="s">
+        <v>884</v>
+      </c>
+      <c r="C83" t="s">
+        <v>885</v>
+      </c>
+      <c r="D83" t="s">
+        <v>494</v>
+      </c>
+      <c r="E83" t="s">
+        <v>19</v>
+      </c>
+      <c r="F83" t="s">
+        <v>886</v>
+      </c>
+      <c r="G83" t="s">
+        <v>887</v>
+      </c>
+      <c r="H83" t="s">
+        <v>626</v>
+      </c>
+      <c r="I83" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" t="s">
+        <v>888</v>
+      </c>
+      <c r="K83" t="s">
+        <v>889</v>
+      </c>
+      <c r="L83" t="s">
+        <v>890</v>
+      </c>
+      <c r="M83" t="s">
+        <v>891</v>
+      </c>
+      <c r="N83" t="s">
+        <v>892</v>
+      </c>
+      <c r="O83" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="84" spans="1:15">
+      <c r="A84" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B84" t="s">
+        <v>894</v>
+      </c>
+      <c r="C84" t="s">
+        <v>895</v>
+      </c>
+      <c r="D84" t="s">
+        <v>18</v>
+      </c>
+      <c r="E84" t="s">
+        <v>19</v>
+      </c>
+      <c r="F84" t="s">
+        <v>896</v>
+      </c>
+      <c r="G84" t="s">
+        <v>297</v>
+      </c>
+      <c r="H84" t="s">
+        <v>897</v>
+      </c>
+      <c r="I84" t="s">
+        <v>19</v>
+      </c>
+      <c r="J84" t="s">
+        <v>898</v>
+      </c>
+      <c r="K84" t="s">
+        <v>626</v>
+      </c>
+      <c r="L84" t="s">
+        <v>899</v>
+      </c>
+      <c r="M84" t="s">
+        <v>344</v>
+      </c>
+      <c r="N84" t="s">
+        <v>719</v>
+      </c>
+      <c r="O84" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="85" spans="1:15">
+      <c r="A85" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B85" t="s">
+        <v>901</v>
+      </c>
+      <c r="C85" t="s">
+        <v>671</v>
+      </c>
+      <c r="D85" t="s">
+        <v>902</v>
+      </c>
+      <c r="E85" t="s">
+        <v>19</v>
+      </c>
+      <c r="F85" t="s">
+        <v>903</v>
+      </c>
+      <c r="G85" t="s">
+        <v>398</v>
+      </c>
+      <c r="H85" t="s">
+        <v>904</v>
+      </c>
+      <c r="I85" t="s">
+        <v>19</v>
+      </c>
+      <c r="J85" t="s">
+        <v>905</v>
+      </c>
+      <c r="K85" t="s">
+        <v>906</v>
+      </c>
+      <c r="L85" t="s">
+        <v>907</v>
+      </c>
+      <c r="M85" t="s">
+        <v>908</v>
+      </c>
+      <c r="N85" t="s">
+        <v>719</v>
+      </c>
+      <c r="O85" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="86" spans="1:15">
+      <c r="A86" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B86" t="s">
+        <v>910</v>
+      </c>
+      <c r="C86" t="s">
+        <v>911</v>
+      </c>
+      <c r="D86" t="s">
+        <v>500</v>
+      </c>
+      <c r="E86" t="s">
+        <v>19</v>
+      </c>
+      <c r="F86" t="s">
+        <v>912</v>
+      </c>
+      <c r="G86" t="s">
+        <v>913</v>
+      </c>
+      <c r="H86" t="s">
+        <v>914</v>
+      </c>
+      <c r="I86" t="s">
+        <v>19</v>
+      </c>
+      <c r="J86" t="s">
+        <v>915</v>
+      </c>
+      <c r="K86" t="s">
+        <v>916</v>
+      </c>
+      <c r="L86" t="s">
+        <v>850</v>
+      </c>
+      <c r="M86" t="s">
+        <v>917</v>
+      </c>
+      <c r="N86" t="s">
+        <v>918</v>
+      </c>
+      <c r="O86" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="87" spans="1:15">
+      <c r="A87" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B87" t="s">
+        <v>920</v>
+      </c>
+      <c r="C87" t="s">
+        <v>921</v>
+      </c>
+      <c r="D87" t="s">
+        <v>296</v>
+      </c>
+      <c r="E87" t="s">
+        <v>19</v>
+      </c>
+      <c r="F87" t="s">
+        <v>922</v>
+      </c>
+      <c r="G87" t="s">
+        <v>923</v>
+      </c>
+      <c r="H87" t="s">
+        <v>513</v>
+      </c>
+      <c r="I87" t="s">
+        <v>19</v>
+      </c>
+      <c r="J87" t="s">
+        <v>924</v>
+      </c>
+      <c r="K87" t="s">
+        <v>925</v>
+      </c>
+      <c r="L87" t="s">
+        <v>332</v>
+      </c>
+      <c r="M87" t="s">
+        <v>926</v>
+      </c>
+      <c r="N87" t="s">
+        <v>927</v>
+      </c>
+      <c r="O87" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15">
+      <c r="A88" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B88" t="s">
+        <v>929</v>
+      </c>
+      <c r="C88" t="s">
+        <v>930</v>
+      </c>
+      <c r="D88" t="s">
+        <v>407</v>
+      </c>
+      <c r="E88" t="s">
+        <v>19</v>
+      </c>
+      <c r="F88" t="s">
+        <v>931</v>
+      </c>
+      <c r="G88" t="s">
+        <v>932</v>
+      </c>
+      <c r="H88" t="s">
+        <v>933</v>
+      </c>
+      <c r="I88" t="s">
+        <v>19</v>
+      </c>
+      <c r="J88" t="s">
+        <v>934</v>
+      </c>
+      <c r="K88" t="s">
+        <v>935</v>
+      </c>
+      <c r="L88" t="s">
+        <v>494</v>
+      </c>
+      <c r="M88" t="s">
+        <v>936</v>
+      </c>
+      <c r="N88" t="s">
+        <v>937</v>
+      </c>
+      <c r="O88" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="89" spans="1:15">
+      <c r="A89" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B89" t="s">
+        <v>939</v>
+      </c>
+      <c r="C89" t="s">
+        <v>940</v>
+      </c>
+      <c r="D89" t="s">
+        <v>771</v>
+      </c>
+      <c r="E89" t="s">
+        <v>19</v>
+      </c>
+      <c r="F89" t="s">
+        <v>941</v>
+      </c>
+      <c r="G89" t="s">
+        <v>942</v>
+      </c>
+      <c r="H89" t="s">
+        <v>943</v>
+      </c>
+      <c r="I89" t="s">
+        <v>19</v>
+      </c>
+      <c r="J89" t="s">
+        <v>944</v>
+      </c>
+      <c r="K89" t="s">
+        <v>945</v>
+      </c>
+      <c r="L89" t="s">
+        <v>225</v>
+      </c>
+      <c r="M89" t="s">
+        <v>946</v>
+      </c>
+      <c r="N89" t="s">
+        <v>719</v>
+      </c>
+      <c r="O89" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="90" spans="1:15">
+      <c r="A90" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B90" t="s">
+        <v>948</v>
+      </c>
+      <c r="C90" t="s">
+        <v>949</v>
+      </c>
+      <c r="D90" t="s">
+        <v>950</v>
+      </c>
+      <c r="E90" t="s">
+        <v>19</v>
+      </c>
+      <c r="F90" t="s">
+        <v>951</v>
+      </c>
+      <c r="G90" t="s">
+        <v>824</v>
+      </c>
+      <c r="H90" t="s">
+        <v>952</v>
+      </c>
+      <c r="I90" t="s">
+        <v>19</v>
+      </c>
+      <c r="J90" t="s">
+        <v>953</v>
+      </c>
+      <c r="K90" t="s">
+        <v>954</v>
+      </c>
+      <c r="L90" t="s">
+        <v>842</v>
+      </c>
+      <c r="M90" t="s">
+        <v>955</v>
+      </c>
+      <c r="N90" t="s">
+        <v>956</v>
+      </c>
+      <c r="O90" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="91" spans="1:15">
+      <c r="A91" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B91" t="s">
+        <v>958</v>
+      </c>
+      <c r="C91" t="s">
+        <v>959</v>
+      </c>
+      <c r="D91" t="s">
+        <v>960</v>
+      </c>
+      <c r="E91" t="s">
+        <v>19</v>
+      </c>
+      <c r="F91" t="s">
+        <v>961</v>
+      </c>
+      <c r="G91" t="s">
+        <v>557</v>
+      </c>
+      <c r="H91" t="s">
+        <v>962</v>
+      </c>
+      <c r="I91" t="s">
+        <v>19</v>
+      </c>
+      <c r="J91" t="s">
+        <v>963</v>
+      </c>
+      <c r="K91" t="s">
+        <v>964</v>
+      </c>
+      <c r="L91" t="s">
+        <v>274</v>
+      </c>
+      <c r="M91" t="s">
+        <v>965</v>
+      </c>
+      <c r="N91" t="s">
+        <v>966</v>
+      </c>
+      <c r="O91" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15">
+      <c r="A92" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B92" t="s">
+        <v>968</v>
+      </c>
+      <c r="C92" t="s">
+        <v>969</v>
+      </c>
+      <c r="D92" t="s">
+        <v>516</v>
+      </c>
+      <c r="E92" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" t="s">
+        <v>970</v>
+      </c>
+      <c r="G92" t="s">
+        <v>907</v>
+      </c>
+      <c r="H92" t="s">
+        <v>971</v>
+      </c>
+      <c r="I92" t="s">
+        <v>19</v>
+      </c>
+      <c r="J92" t="s">
+        <v>972</v>
+      </c>
+      <c r="K92" t="s">
+        <v>582</v>
+      </c>
+      <c r="L92" t="s">
+        <v>320</v>
+      </c>
+      <c r="M92" t="s">
+        <v>973</v>
+      </c>
+      <c r="N92" t="s">
+        <v>974</v>
+      </c>
+      <c r="O92" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="93" spans="1:15">
+      <c r="A93" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B93" t="s">
+        <v>976</v>
+      </c>
+      <c r="C93" t="s">
+        <v>671</v>
+      </c>
+      <c r="D93" t="s">
+        <v>703</v>
+      </c>
+      <c r="E93" t="s">
+        <v>19</v>
+      </c>
+      <c r="F93" t="s">
+        <v>977</v>
+      </c>
+      <c r="G93" t="s">
+        <v>425</v>
+      </c>
+      <c r="H93" t="s">
+        <v>978</v>
+      </c>
+      <c r="I93" t="s">
+        <v>19</v>
+      </c>
+      <c r="J93" t="s">
+        <v>979</v>
+      </c>
+      <c r="K93" t="s">
+        <v>980</v>
+      </c>
+      <c r="L93" t="s">
+        <v>332</v>
+      </c>
+      <c r="M93" t="s">
+        <v>981</v>
+      </c>
+      <c r="N93" t="s">
+        <v>982</v>
+      </c>
+      <c r="O93" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15">
+      <c r="A94" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B94" t="s">
+        <v>984</v>
+      </c>
+      <c r="C94" t="s">
+        <v>985</v>
+      </c>
+      <c r="D94" t="s">
+        <v>986</v>
+      </c>
+      <c r="E94" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" t="s">
+        <v>987</v>
+      </c>
+      <c r="G94" t="s">
+        <v>988</v>
+      </c>
+      <c r="H94" t="s">
+        <v>989</v>
+      </c>
+      <c r="I94" t="s">
+        <v>19</v>
+      </c>
+      <c r="J94" t="s">
+        <v>990</v>
+      </c>
+      <c r="K94" t="s">
+        <v>545</v>
+      </c>
+      <c r="L94" t="s">
+        <v>991</v>
+      </c>
+      <c r="M94" t="s">
+        <v>992</v>
+      </c>
+      <c r="N94" t="s">
+        <v>993</v>
+      </c>
+      <c r="O94" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="95" spans="1:15">
+      <c r="A95" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B95" t="s">
+        <v>995</v>
+      </c>
+      <c r="C95" t="s">
+        <v>671</v>
+      </c>
+      <c r="D95" t="s">
+        <v>567</v>
+      </c>
+      <c r="E95" t="s">
+        <v>19</v>
+      </c>
+      <c r="F95" t="s">
+        <v>996</v>
+      </c>
+      <c r="G95" t="s">
+        <v>997</v>
+      </c>
+      <c r="H95" t="s">
+        <v>998</v>
+      </c>
+      <c r="I95" t="s">
+        <v>19</v>
+      </c>
+      <c r="J95" t="s">
+        <v>999</v>
+      </c>
+      <c r="K95" t="s">
+        <v>119</v>
+      </c>
+      <c r="L95" t="s">
+        <v>1000</v>
+      </c>
+      <c r="M95" t="s">
+        <v>1001</v>
+      </c>
+      <c r="N95" t="s">
+        <v>1002</v>
+      </c>
+      <c r="O95" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15">
+      <c r="A96" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B96" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C96" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D96" t="s">
+        <v>766</v>
+      </c>
+      <c r="E96" t="s">
+        <v>19</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1006</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H96" t="s">
+        <v>1008</v>
+      </c>
+      <c r="I96" t="s">
+        <v>19</v>
+      </c>
+      <c r="J96" t="s">
+        <v>1009</v>
+      </c>
+      <c r="K96" t="s">
+        <v>1010</v>
+      </c>
+      <c r="L96" t="s">
+        <v>717</v>
+      </c>
+      <c r="M96" t="s">
+        <v>472</v>
+      </c>
+      <c r="N96" t="s">
+        <v>1011</v>
+      </c>
+      <c r="O96" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="97" spans="1:15">
+      <c r="A97" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B97" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C97" t="s">
+        <v>671</v>
+      </c>
+      <c r="D97" t="s">
+        <v>424</v>
+      </c>
+      <c r="E97" t="s">
+        <v>19</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1016</v>
+      </c>
+      <c r="I97" t="s">
+        <v>19</v>
+      </c>
+      <c r="J97" t="s">
+        <v>1017</v>
+      </c>
+      <c r="K97" t="s">
+        <v>763</v>
+      </c>
+      <c r="L97" t="s">
+        <v>1018</v>
+      </c>
+      <c r="M97" t="s">
+        <v>1019</v>
+      </c>
+      <c r="N97" t="s">
+        <v>1020</v>
+      </c>
+      <c r="O97" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15">
+      <c r="A98" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B98" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C98" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E98" t="s">
+        <v>19</v>
+      </c>
+      <c r="F98" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G98" t="s">
+        <v>813</v>
+      </c>
+      <c r="H98" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I98" t="s">
+        <v>19</v>
+      </c>
+      <c r="J98" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K98" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L98" t="s">
+        <v>1029</v>
+      </c>
+      <c r="M98" t="s">
+        <v>1030</v>
+      </c>
+      <c r="N98" t="s">
+        <v>1031</v>
+      </c>
+      <c r="O98" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15">
+      <c r="A99" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B99" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C99" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D99" t="s">
+        <v>991</v>
+      </c>
+      <c r="E99" t="s">
+        <v>19</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I99" t="s">
+        <v>19</v>
+      </c>
+      <c r="J99" t="s">
+        <v>1038</v>
+      </c>
+      <c r="K99" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L99" t="s">
+        <v>1040</v>
+      </c>
+      <c r="M99" t="s">
+        <v>1041</v>
+      </c>
+      <c r="N99" t="s">
+        <v>1042</v>
+      </c>
+      <c r="O99" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15">
+      <c r="A100" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B100" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C100" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D100" t="s">
+        <v>500</v>
+      </c>
+      <c r="E100" t="s">
+        <v>19</v>
+      </c>
+      <c r="F100" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H100" t="s">
+        <v>380</v>
+      </c>
+      <c r="I100" t="s">
+        <v>19</v>
+      </c>
+      <c r="J100" t="s">
+        <v>1048</v>
+      </c>
+      <c r="K100" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L100" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M100" t="s">
+        <v>1051</v>
+      </c>
+      <c r="N100" t="s">
+        <v>1052</v>
+      </c>
+      <c r="O100" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="101" spans="1:15">
+      <c r="A101" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C101" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D101" t="s">
+        <v>587</v>
+      </c>
+      <c r="E101" t="s">
+        <v>19</v>
+      </c>
+      <c r="F101" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G101" t="s">
+        <v>39</v>
+      </c>
+      <c r="H101" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I101" t="s">
+        <v>19</v>
+      </c>
+      <c r="J101" t="s">
+        <v>1058</v>
+      </c>
+      <c r="K101" t="s">
+        <v>840</v>
+      </c>
+      <c r="L101" t="s">
+        <v>1059</v>
+      </c>
+      <c r="M101" t="s">
+        <v>1060</v>
+      </c>
+      <c r="N101" t="s">
+        <v>1061</v>
+      </c>
+      <c r="O101" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="102" spans="1:15">
+      <c r="A102" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C102" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E102" t="s">
+        <v>19</v>
+      </c>
+      <c r="F102" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G102" t="s">
+        <v>1067</v>
+      </c>
+      <c r="H102" t="s">
+        <v>472</v>
+      </c>
+      <c r="I102" t="s">
+        <v>19</v>
+      </c>
+      <c r="J102" t="s">
+        <v>1068</v>
+      </c>
+      <c r="K102" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L102" t="s">
+        <v>488</v>
+      </c>
+      <c r="M102" t="s">
+        <v>1070</v>
+      </c>
+      <c r="N102" t="s">
+        <v>1071</v>
+      </c>
+      <c r="O102" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="103" spans="1:15">
+      <c r="A103" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B103" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C103" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E103" t="s">
+        <v>19</v>
+      </c>
+      <c r="F103" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G103" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H103" t="s">
+        <v>1078</v>
+      </c>
+      <c r="I103" t="s">
+        <v>19</v>
+      </c>
+      <c r="J103" t="s">
+        <v>1079</v>
+      </c>
+      <c r="K103" t="s">
+        <v>1080</v>
+      </c>
+      <c r="L103" t="s">
+        <v>1081</v>
+      </c>
+      <c r="M103" t="s">
+        <v>1082</v>
+      </c>
+      <c r="N103" t="s">
+        <v>1083</v>
+      </c>
+      <c r="O103" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15">
+      <c r="A104" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B104" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C104" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E104" t="s">
+        <v>19</v>
+      </c>
+      <c r="F104" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G104" t="s">
+        <v>850</v>
+      </c>
+      <c r="H104" t="s">
+        <v>743</v>
+      </c>
+      <c r="I104" t="s">
+        <v>19</v>
+      </c>
+      <c r="J104" t="s">
+        <v>1089</v>
+      </c>
+      <c r="K104" t="s">
+        <v>1090</v>
+      </c>
+      <c r="L104" t="s">
+        <v>1091</v>
+      </c>
+      <c r="M104" t="s">
+        <v>1092</v>
+      </c>
+      <c r="N104" t="s">
+        <v>1093</v>
+      </c>
+      <c r="O104" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="105" spans="1:15">
+      <c r="A105" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B105" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C105" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E105" t="s">
+        <v>19</v>
+      </c>
+      <c r="F105" t="s">
+        <v>1098</v>
+      </c>
+      <c r="G105" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H105" t="s">
+        <v>513</v>
+      </c>
+      <c r="I105" t="s">
+        <v>19</v>
+      </c>
+      <c r="J105" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K105" t="s">
+        <v>537</v>
+      </c>
+      <c r="L105" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M105" t="s">
+        <v>1102</v>
+      </c>
+      <c r="N105" t="s">
+        <v>1103</v>
+      </c>
+      <c r="O105" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:15">
+      <c r="A106" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B106" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C106" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E106" t="s">
+        <v>19</v>
+      </c>
+      <c r="F106" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G106" t="s">
+        <v>860</v>
+      </c>
+      <c r="H106" t="s">
+        <v>513</v>
+      </c>
+      <c r="I106" t="s">
+        <v>19</v>
+      </c>
+      <c r="J106" t="s">
+        <v>1109</v>
+      </c>
+      <c r="K106" t="s">
+        <v>1110</v>
+      </c>
+      <c r="L106" t="s">
+        <v>1111</v>
+      </c>
+      <c r="M106" t="s">
+        <v>1112</v>
+      </c>
+      <c r="N106" t="s">
+        <v>1113</v>
+      </c>
+      <c r="O106" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:15">
+      <c r="A107" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B107" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C107" t="s">
+        <v>671</v>
+      </c>
+      <c r="D107" t="s">
+        <v>698</v>
+      </c>
+      <c r="E107" t="s">
+        <v>19</v>
+      </c>
+      <c r="F107" t="s">
+        <v>390</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H107" t="s">
+        <v>1117</v>
+      </c>
+      <c r="I107" t="s">
+        <v>19</v>
+      </c>
+      <c r="J107" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K107" t="s">
+        <v>1119</v>
+      </c>
+      <c r="L107" t="s">
+        <v>332</v>
+      </c>
+      <c r="M107" t="s">
+        <v>1120</v>
+      </c>
+      <c r="N107" t="s">
+        <v>1121</v>
+      </c>
+      <c r="O107" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="108" spans="1:15">
+      <c r="A108" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B108" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C108" t="s">
+        <v>1124</v>
+      </c>
+      <c r="D108" t="s">
+        <v>828</v>
+      </c>
+      <c r="E108" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G108" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H108" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I108" t="s">
+        <v>19</v>
+      </c>
+      <c r="J108" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K108" t="s">
+        <v>1129</v>
+      </c>
+      <c r="L108" t="s">
+        <v>332</v>
+      </c>
+      <c r="M108" t="s">
+        <v>45</v>
+      </c>
+      <c r="N108" t="s">
+        <v>1130</v>
+      </c>
+      <c r="O108" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="109" spans="1:15">
+      <c r="A109" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B109" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C109" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E109" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G109" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H109" t="s">
+        <v>513</v>
+      </c>
+      <c r="I109" t="s">
+        <v>19</v>
+      </c>
+      <c r="J109" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K109" t="s">
+        <v>316</v>
+      </c>
+      <c r="L109" t="s">
+        <v>1138</v>
+      </c>
+      <c r="M109" t="s">
+        <v>1139</v>
+      </c>
+      <c r="N109" t="s">
+        <v>1140</v>
+      </c>
+      <c r="O109" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="110" spans="1:15">
+      <c r="A110" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C110" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D110" t="s">
+        <v>500</v>
+      </c>
+      <c r="E110" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G110" t="s">
+        <v>420</v>
+      </c>
+      <c r="H110" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I110" t="s">
+        <v>19</v>
+      </c>
+      <c r="J110" t="s">
+        <v>665</v>
+      </c>
+      <c r="K110" t="s">
+        <v>296</v>
+      </c>
+      <c r="L110" t="s">
+        <v>752</v>
+      </c>
+      <c r="M110" t="s">
+        <v>1146</v>
+      </c>
+      <c r="N110" t="s">
+        <v>1147</v>
+      </c>
+      <c r="O110" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="111" spans="1:15">
+      <c r="A111" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B111" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C111" t="s">
+        <v>1150</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E111" t="s">
+        <v>19</v>
+      </c>
+      <c r="F111" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G111" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H111" t="s">
+        <v>1153</v>
+      </c>
+      <c r="I111" t="s">
+        <v>19</v>
+      </c>
+      <c r="J111" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K111" t="s">
+        <v>144</v>
+      </c>
+      <c r="L111" t="s">
+        <v>1065</v>
+      </c>
+      <c r="M111" t="s">
+        <v>1155</v>
+      </c>
+      <c r="N111" t="s">
+        <v>1156</v>
+      </c>
+      <c r="O111" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="112" spans="1:15">
+      <c r="A112" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B112" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C112" t="s">
+        <v>1159</v>
+      </c>
+      <c r="D112" t="s">
+        <v>354</v>
+      </c>
+      <c r="E112" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G112" t="s">
+        <v>811</v>
+      </c>
+      <c r="H112" t="s">
+        <v>1161</v>
+      </c>
+      <c r="I112" t="s">
+        <v>19</v>
+      </c>
+      <c r="J112" t="s">
+        <v>1162</v>
+      </c>
+      <c r="K112" t="s">
+        <v>1163</v>
+      </c>
+      <c r="L112" t="s">
+        <v>816</v>
+      </c>
+      <c r="M112" t="s">
+        <v>1164</v>
+      </c>
+      <c r="N112" t="s">
+        <v>1165</v>
+      </c>
+      <c r="O112" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="113" spans="1:15">
+      <c r="A113" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C113" t="s">
+        <v>1168</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E113" t="s">
+        <v>19</v>
+      </c>
+      <c r="F113" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G113" t="s">
+        <v>663</v>
+      </c>
+      <c r="H113" t="s">
+        <v>84</v>
+      </c>
+      <c r="I113" t="s">
+        <v>19</v>
+      </c>
+      <c r="J113" t="s">
+        <v>1171</v>
+      </c>
+      <c r="K113" t="s">
+        <v>1172</v>
+      </c>
+      <c r="L113" t="s">
+        <v>354</v>
+      </c>
+      <c r="M113" t="s">
+        <v>1173</v>
+      </c>
+      <c r="N113" t="s">
+        <v>1174</v>
+      </c>
+      <c r="O113" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="114" spans="1:15">
+      <c r="A114" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B114" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C114" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D114" t="s">
+        <v>500</v>
+      </c>
+      <c r="E114" t="s">
+        <v>19</v>
+      </c>
+      <c r="F114" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G114" t="s">
+        <v>960</v>
+      </c>
+      <c r="H114" t="s">
+        <v>1179</v>
+      </c>
+      <c r="I114" t="s">
+        <v>19</v>
+      </c>
+      <c r="J114" t="s">
+        <v>1180</v>
+      </c>
+      <c r="K114" t="s">
+        <v>316</v>
+      </c>
+      <c r="L114" t="s">
+        <v>766</v>
+      </c>
+      <c r="M114" t="s">
+        <v>1181</v>
+      </c>
+      <c r="N114" t="s">
+        <v>1182</v>
+      </c>
+      <c r="O114" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="115" spans="1:15">
+      <c r="A115" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C115" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D115" t="s">
+        <v>656</v>
+      </c>
+      <c r="E115" t="s">
+        <v>19</v>
+      </c>
+      <c r="F115" t="s">
+        <v>533</v>
+      </c>
+      <c r="G115" t="s">
+        <v>816</v>
+      </c>
+      <c r="H115" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I115" t="s">
+        <v>19</v>
+      </c>
+      <c r="J115" t="s">
+        <v>1187</v>
+      </c>
+      <c r="K115" t="s">
+        <v>678</v>
+      </c>
+      <c r="L115" t="s">
+        <v>341</v>
+      </c>
+      <c r="M115" t="s">
+        <v>1188</v>
+      </c>
+      <c r="N115" t="s">
+        <v>1189</v>
+      </c>
+      <c r="O115" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="116" spans="1:15">
+      <c r="A116" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C116" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D116" t="s">
+        <v>500</v>
+      </c>
+      <c r="E116" t="s">
+        <v>19</v>
+      </c>
+      <c r="F116" t="s">
+        <v>627</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H116" t="s">
+        <v>1194</v>
+      </c>
+      <c r="I116" t="s">
+        <v>19</v>
+      </c>
+      <c r="J116" t="s">
+        <v>1195</v>
+      </c>
+      <c r="K116" t="s">
+        <v>1196</v>
+      </c>
+      <c r="L116" t="s">
+        <v>1197</v>
+      </c>
+      <c r="M116" t="s">
+        <v>226</v>
+      </c>
+      <c r="N116" t="s">
+        <v>1198</v>
+      </c>
+      <c r="O116" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="117" spans="1:15">
+      <c r="A117" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C117" t="s">
+        <v>671</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E117" t="s">
+        <v>19</v>
+      </c>
+      <c r="F117" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G117" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H117" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I117" t="s">
+        <v>19</v>
+      </c>
+      <c r="J117" t="s">
+        <v>1205</v>
+      </c>
+      <c r="K117" t="s">
+        <v>218</v>
+      </c>
+      <c r="L117" t="s">
+        <v>296</v>
+      </c>
+      <c r="M117" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N117" t="s">
+        <v>1207</v>
+      </c>
+      <c r="O117" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15">
+      <c r="A118" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C118" t="s">
+        <v>671</v>
+      </c>
+      <c r="D118" t="s">
+        <v>401</v>
+      </c>
+      <c r="E118" t="s">
+        <v>19</v>
+      </c>
+      <c r="F118" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G118" t="s">
+        <v>276</v>
+      </c>
+      <c r="H118" t="s">
+        <v>1211</v>
+      </c>
+      <c r="I118" t="s">
+        <v>19</v>
+      </c>
+      <c r="J118" t="s">
+        <v>1212</v>
+      </c>
+      <c r="K118" t="s">
+        <v>37</v>
+      </c>
+      <c r="L118" t="s">
+        <v>1213</v>
+      </c>
+      <c r="M118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="N118" t="s">
+        <v>1215</v>
+      </c>
+      <c r="O118" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="119" spans="1:15">
+      <c r="A119" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C119" t="s">
+        <v>671</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1218</v>
+      </c>
+      <c r="E119" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G119" t="s">
+        <v>744</v>
+      </c>
+      <c r="H119" t="s">
+        <v>1220</v>
+      </c>
+      <c r="I119" t="s">
+        <v>19</v>
+      </c>
+      <c r="J119" t="s">
+        <v>1221</v>
+      </c>
+      <c r="K119" t="s">
+        <v>1222</v>
+      </c>
+      <c r="L119" t="s">
+        <v>733</v>
+      </c>
+      <c r="M119" t="s">
+        <v>1223</v>
+      </c>
+      <c r="N119" t="s">
+        <v>1224</v>
+      </c>
+      <c r="O119" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="120" spans="1:15">
+      <c r="A120" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C120" t="s">
+        <v>1227</v>
+      </c>
+      <c r="D120" t="s">
+        <v>537</v>
+      </c>
+      <c r="E120" t="s">
+        <v>19</v>
+      </c>
+      <c r="F120" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G120" t="s">
+        <v>1229</v>
+      </c>
+      <c r="H120" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I120" t="s">
+        <v>19</v>
+      </c>
+      <c r="J120" t="s">
+        <v>1231</v>
+      </c>
+      <c r="K120" t="s">
+        <v>1232</v>
+      </c>
+      <c r="L120" t="s">
+        <v>1233</v>
+      </c>
+      <c r="M120" t="s">
+        <v>1234</v>
+      </c>
+      <c r="N120" t="s">
+        <v>1235</v>
+      </c>
+      <c r="O120" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="121" spans="1:15">
+      <c r="A121" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C121" t="s">
+        <v>671</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E121" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" t="s">
+        <v>1239</v>
+      </c>
+      <c r="G121" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H121" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I121" t="s">
+        <v>19</v>
+      </c>
+      <c r="J121" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K121" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L121" t="s">
+        <v>1101</v>
+      </c>
+      <c r="M121" t="s">
+        <v>1244</v>
+      </c>
+      <c r="N121" t="s">
+        <v>1245</v>
+      </c>
+      <c r="O121" t="s">
+        <v>1246</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>